--- a/src/conf/cross_sector_insight/cross_sector_insights.xlsx
+++ b/src/conf/cross_sector_insight/cross_sector_insights.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11060" firstSheet="3" activeTab="7"/>
+    <workbookView windowWidth="28000" windowHeight="11060" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="cross_sector_insights_tp" sheetId="4" r:id="rId1"/>
@@ -15,6 +15,7 @@
     <sheet name="s002_insights" sheetId="2" r:id="rId6"/>
     <sheet name="s003_insights" sheetId="1" r:id="rId7"/>
     <sheet name="pattern type" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cross_sector_insights_tp!$A$1:$H$16</definedName>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="380">
   <si>
     <t>ID</t>
   </si>
@@ -97,6 +98,13 @@
     <t>Digital Codification</t>
   </si>
   <si>
+    <t>&lt;TP01, TK06&gt;</t>
+  </si>
+  <si>
+    <t>&lt;TP01, TK05&gt;
+&lt;TP01, TK10&gt;</t>
+  </si>
+  <si>
     <t>TP02</t>
   </si>
   <si>
@@ -118,6 +126,19 @@
     <t>Experiential Amplification</t>
   </si>
   <si>
+    <t>&lt;TP03, TK05&gt;
+&lt;TP03, TK06&gt;</t>
+  </si>
+  <si>
+    <t>&lt;TP03, TK07&gt;
+&lt;TP03, TK08&gt;
+&lt;TP03, TK10&gt;</t>
+  </si>
+  <si>
+    <t>&lt;TP03, TK04&gt;
+&lt;TP03, TK11&gt;</t>
+  </si>
+  <si>
     <t>TP04</t>
   </si>
   <si>
@@ -145,6 +166,10 @@
     <t>Uses IMUs, wearable sensors, eye trackers, cameras, and video analysis to record workers’ movement, posture, gaze, workload, task sequences, and situated work activities.</t>
   </si>
   <si>
+    <t>&lt;TP06, TK06&gt;
+&lt;TP06, TK07&gt;</t>
+  </si>
+  <si>
     <t>TP07</t>
   </si>
   <si>
@@ -154,6 +179,12 @@
     <t>Uses AI, machine learning, NLP, statistical learning, or rule-based algorithms to derive classifications, forecasts, detected patterns, and predicted conditions from data.</t>
   </si>
   <si>
+    <t>&lt;TP07, TK06&gt;</t>
+  </si>
+  <si>
+    <t>&lt;TP07, TK10&gt;</t>
+  </si>
+  <si>
     <t>TP08</t>
   </si>
   <si>
@@ -163,6 +194,9 @@
     <t>Uses generative AI to combine requirements, contextual data, and retrieved knowledge into new drafts, reports, explanations, summaries, or recommendations.</t>
   </si>
   <si>
+    <t>&lt;TP08, TK12&gt;</t>
+  </si>
+  <si>
     <t>TP09</t>
   </si>
   <si>
@@ -172,6 +206,9 @@
     <t>Uses knowledge graphs, semantic metadata, embeddings, vector databases, and meaning-based search to represent knowledge relationships and retrieve contextually relevant information.</t>
   </si>
   <si>
+    <t>&lt;TP09, TK05&gt;</t>
+  </si>
+  <si>
     <t>TP10</t>
   </si>
   <si>
@@ -181,6 +218,10 @@
     <t>Preserves and retrieves codified project records, narratives, lessons learned, safety information, and operational knowledge through databases, data warehouses, or conventional KMS repositories.</t>
   </si>
   <si>
+    <t>&lt;TP10, TK04&gt;
+&lt;TP10, TK05&gt;</t>
+  </si>
+  <si>
     <t>TP11</t>
   </si>
   <si>
@@ -190,6 +231,9 @@
     <t>Uses portals, messaging systems, shared virtual environments, and online collaboration platforms to support peer exchange, collective interpretation, user contribution, and shared knowledge construction.</t>
   </si>
   <si>
+    <t>&lt;TP11, TK04&gt;</t>
+  </si>
+  <si>
     <t>TP12</t>
   </si>
   <si>
@@ -199,6 +243,9 @@
     <t>Combines digital content, interactive media, online resources, and face-to-face or workplace activities to strengthen demonstration, participation, and knowledge internalization.</t>
   </si>
   <si>
+    <t>&lt;TP12, TK05&gt;</t>
+  </si>
+  <si>
     <t>TP13</t>
   </si>
   <si>
@@ -206,6 +253,9 @@
   </si>
   <si>
     <t>Measures, compares, scores, or ranks learners, models, interventions, and alternatives using predefined criteria, indicators, benchmarks, or performance metrics.</t>
+  </si>
+  <si>
+    <t>&lt;TP13, TK10&gt;</t>
   </si>
   <si>
     <t>TP15</t>
@@ -881,7 +931,7 @@
   </si>
   <si>
     <t>TK02 Knowledge Conveyed Through Examples or Demonstration
-TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment
 TK11 Informal Coordination, Communication, and Escalation Know-how
@@ -938,7 +988,7 @@
     <t>Extended-reality technologies retain tacit knowledge by placing learners inside consequential work situations. AR, mixed reality, imaging, and sensing overlay expert instructions, components, and cues onto physical tasks, allowing users to observe, act, receive feedback, and repeat procedures. Assembly and machinery cases show improved positioning, procedural performance, perceptual recognition, and autonomous execution. The dominant mechanism is Experience Amplification because knowledge is stabilized through embodied rehearsal rather than preserved mainly as an external record. Retention nevertheless depends on instructional quality, usable interfaces, trainer intervention, realistic context, repeated practice, and delayed assessment; technical adoption alone does not demonstrate durable transfer to workplace performance.</t>
   </si>
   <si>
-    <t>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+    <t>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</t>
@@ -978,7 +1028,7 @@
     <t>Collaborative digital platforms retain tacit knowledge by enabling participants to contribute experience, interpret problems, negotiate meaning, and develop shared practices. Artificial intelligence, immersive interfaces, connected systems, and knowledge platforms create spaces where unarticulated know-how, professional language, and unwritten organizational norms become encounterable through interaction. The dominant mechanism is Experience Amplification because retention occurs principally through dialogue, participation, and collective sensemaking; stored messages or records play a supporting role. Effective retention depends on trust, psychological safety, inclusive participation, familiarity, governance, and workflow integration. Without sustained contribution and application, technical connectivity produces information exchange but not durable shared understanding or organizational capability.</t>
   </si>
   <si>
-    <t>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+    <t>TK04 Unrecognized or Unarticulated Personal Know-how
 TK09 Shared Professional Language and Contextual Meaning
 TK12 Organizational Culture and Unwritten Working Practices</t>
   </si>
@@ -1060,7 +1110,7 @@
   </si>
   <si>
     <t>TK02 Knowledge Conveyed Through Examples or Demonstration
-TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</t>
   </si>
@@ -1121,7 +1171,7 @@
     <t>AI-supported archiving technologies retain tacit knowledge by converting project experience into organizational records. Tools help elicit, classify, summarize, and store unarticulated know-how and practised motor or operational skills within repositories. The dominant mechanism is Digital Codification because experience is externalized as structured content that can remain available after the original holder leaves. Archives can improve continuity and provide examples for work, but storage alone does not preserve contextual meaning or guarantee reuse. Effective retention depends on trustworthy elicitation, expert validation, appropriate metadata, privacy controls, stewardship, accessible retrieval, and organizational routines that translate archived material back into situated judgment and performance.</t>
   </si>
   <si>
-    <t>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+    <t>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill</t>
   </si>
   <si>
@@ -1354,6 +1404,9 @@
   </si>
   <si>
     <t>Purpose / theoretical value</t>
+  </si>
+  <si>
+    <t>Cypher</t>
   </si>
   <si>
     <t>Cross-sector TP–TK convergence</t>
@@ -1388,6 +1441,161 @@
     </r>
   </si>
   <si>
+    <t>MATCH (tp:TechnologyenablePractice)-[r]-(b:TacitKnowledge|EnvironmentalDependency|OrganizationalDependency|Limitation) 
+WHERE tp.node_id = 'h001M01TP03' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, COLLECT({src_node:tp, rel: r, dst_node: b}) AS tpBy,
+COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,tp_child_By,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
+COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tp_r_child_list
+WITH tp, tpBy,tp_child_By,tp_r_child_by,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS childBy
+RETURN tp, tpBy,tp_child_By,childBy,tp_r_child_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
+***Task***
+Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that &lt;TP03, TK06&gt; belongs to this pattern type.
+- Name: Cross-sector TP–TK convergence
+- Definition:  A comparable TP is associated with comparable TK forms across all three sectors. 
+- Purpose: Identifies the strongest evidence of a cross-sector common retention configuration and helps reveal what may transcend sector boundaries at both the practice and knowledge-target levels.
+***Input data***
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+MATCH (tp:TechnologyenablePractice)-[r]-(b:TacitKnowledge|EnvironmentalDependency|OrganizationalDependency|Limitation) 
+WHERE tp.node_id = 'h001M01TP03' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, COLLECT({src_node:tp, rel: r, dst_node: b}) AS tpBy,
+COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,tp_child_By,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
+COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tp_r_child_list
+WITH tp, tpBy,tp_child_By,tp_r_child_by,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS childBy
+RETURN tp, tpBy,tp_child_By,childBy,tp_r_child_by
+***Output Structure***
+Pattern Name: TP03 Situated Experiential Learning through Extended Reality
+Pattern Type: Cross-sector TP–TK convergence
+Technology-enable Practice Definition: Uses technologies like VR, AR, MR, CAVE, or hybrid XR environments to support embodied rehearsal, contextual guidance, historical interpretation, hazard recognition, and situated knowledge transfer.
+Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP03 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node&gt;  
+Inspiring Cues:
+Resource and Capability Dependencies:
+Organizational Culture Dependencies:
+</t>
+  </si>
+  <si>
+    <t>&lt;TP03,TK06&gt;</t>
+  </si>
+  <si>
+    <t>MATCH (tp:TechnologyenablePractice)-[r]-(tk:TacitKnowledge) 
+WHERE tp.node_id = 'h001M01TP03' AND tk.node_id = 'h001M01TK06'
+WITH tp, COLLECT({src_node:tp, rel: r, dst_node: tk}) AS tp_tk_By,
+COLLECT(DISTINCT tk) AS tp_tk_list
+OPTIONAL MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE (a = tp OR a in tp_tk_list) AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tp_tk_By, tp_tk_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_By,
+COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tp_tk_By, tp_tk_list, tp_r_By,tp_r_list,
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_tk_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_child_by,
+COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
+COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tp_r_child_list
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_childBy
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tk_child_list AND b in tp_r_child_list
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,tp_r_childBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_r_childBy
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tk_child_list
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, tk_r_childBy,tp_r_childBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_tk_childBy
+RETURN tp, tp_tk_By,tp_child_By,tk_child_by,tp_r_child_by,tk_r_childBy,tp_r_childBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
+***Task***
+Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that &lt;TP03, TK06&gt; belongs to this pattern type.
+- Name: Cross-sector TP–TK convergence
+- Definition:  A comparable TP is associated with comparable TK forms across all three sectors. 
+- Purpose: Identifies the strongest evidence of a cross-sector common retention configuration and helps reveal what may transcend sector boundaries at both the practice and knowledge-target levels.
+***Input data***
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+MATCH (tp:TechnologyenablePractice)-[r]-(tk:TacitKnowledge) 
+WHERE tp.node_id = 'h001M01TP03' AND tk.node_id = 'h001M01TK06'
+WITH tp, COLLECT({src_node:tp, rel: r, dst_node: tk}) AS tp_tk_By,
+COLLECT(DISTINCT tk) AS tp_tk_list
+OPTIONAL MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE (a = tp OR a in tp_tk_list) AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tp_tk_By, tp_tk_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_By,
+COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tp_tk_By, tp_tk_list, tp_r_By,tp_r_list,
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_tk_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_child_by,
+COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
+COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tp_r_child_list
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_childBy
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tk_child_list AND b in tp_r_child_list
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,tp_r_childBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_r_childBy
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tk_child_list
+WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, tk_r_childBy,tp_r_childBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_tk_childBy
+RETURN tp, tp_tk_By,tp_child_By,tk_child_by,tp_r_child_by,tk_r_childBy,tp_r_childBy
+***Output Structure***
+Pattern Name: &lt;TP03, TK06&gt;  &lt;please name it&gt;
+Pattern Type: Cross-sector TP–TK convergence
+Technology-enable Practice Definition: Uses technologies like VR, AR, MR, CAVE, or hybrid XR environments to support embodied rehearsal, contextual guidance, historical interpretation, hazard recognition, and situated knowledge transfer.
+Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP03 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node&gt;  
+Inspiring Cues:
+</t>
+  </si>
+  <si>
     <t>Context-bounded TP–TK convergence</t>
   </si>
   <si>
@@ -1420,6 +1628,63 @@
     </r>
   </si>
   <si>
+    <t>MATCH (tp:TechnologyenablePractice)-[r]-(b:TacitKnowledge|EnvironmentalDependency|OrganizationalDependency|Limitation) 
+WHERE tp.node_id = 'h001M01TP15' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, COLLECT({src_node:tp, rel: r, dst_node: b}) AS tpBy,
+COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,tp_child_By,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
+COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tp_r_child_list
+WITH tp, tpBy,tp_child_By,tp_r_child_by,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS childBy
+RETURN tp, tpBy,tp_child_By,childBy,tp_r_child_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
+***Task***
+Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that TP15 belongs to this pattern type.
+- Name: Context-bounded TP–TK convergence
+- Definition:  A comparable TP is associated with comparable TK forms within a sector pair or a particular sector configuration, but this convergence is not observed across all three sectors.
+- Purpose: Identifies bounded commonality, showing that some retention configurations may be shared between particular contexts rather than being broadly cross-sector. This helps establish the boundary conditions of apparent generality.
+***Input data***
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+MATCH (tp:TechnologyenablePractice)-[r]-(b:TacitKnowledge|EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE tp.node_id = 'h001M01TP15' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, COLLECT({src_node:tp, rel: r, dst_node: b}) AS tpBy,
+COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tp, tpBy,tp_r_list,tp_child_By,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
+COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tp_r_child_list
+WITH tp, tpBy,tp_child_By,tp_r_child_by,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS childBy
+RETURN tp, tpBy,tp_child_By,childBy,tp_r_child_by
+***Output Structure***
+Pattern Name: TP15 Distributed-Ledger-enabled Transaction Assurance and Traceability
+Pattern Type: Context-bounded TP–TK convergence
+Technology-enable Practice Definition: Uses blockchain or distributed-ledger technologies to create verifiable transaction records, strengthen provenance and supply-chain traceability, validate products, and automate trusted exchanges through smart contracts or related mechanisms.
+Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP10 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node&gt;  
+Inspiring Cues:
+</t>
+  </si>
+  <si>
     <t>TK variation across TPs</t>
   </si>
   <si>
@@ -1451,6 +1716,275 @@
       <t xml:space="preserve"> through which a similar tacit-knowledge retention target may be addressed, revealing that a knowledge-retention need is not necessarily tied to one technological practice.</t>
     </r>
   </si>
+  <si>
+    <t>MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+WHERE tk.node_id = 'h001M01TK05' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, COLLECT({src_node:tk, rel: r, dst_node: b}) AS tpBy,
+COLLECT(DISTINCT b) AS tp_list
+OPTIONAL MATCH (tp)-[r]-(b:EnvironmentalDependency|Limitation|OrganizationalDependency) 
+WHERE tp in tp_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy, tp_list, 
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS depBy,
+COLLECT(DISTINCT b) AS dep_list
+OPTIONAL MATCH (tk)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy,tp_list,depBy,dep_list,
+COLLECT({src_node:tk, rel: r, dst_node: b}) AS tk_child_By,
+COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy, tk_child_By,depBy,dep_list,tp_list,tk_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_child_by,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in dep_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy, tk_child_By,depBy,dep_list,tp_list,tk_child_list,tp_child_by,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_child_by,
+COLLECT(DISTINCT b) AS dep_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tk_child_list
+WITH tk, tpBy, tk_child_By,tp_child_by,dep_child_by,dep_child_list,depBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS childBy,
+COLLECT(DISTINCT a) AS tp_child_list,
+COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in dep_child_list
+WITH tk, tpBy, tk_child_By,tp_child_by,dep_child_by,childBy,depBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_childBy
+RETURN tk, tpBy,tk_child_By,tp_child_by,childBy,dep_childBy,depBy</t>
+  </si>
+  <si>
+    <t>You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
+***Task***
+Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that TK05 belongs to this pattern type.
+- Name: TK variation across TPs
+- Definition: A comparable TK form is associated with different TPs across the selected evidence. 
+- Purpose: Identifies alternative practice pathways through which a similar tacit-knowledge retention target may be addressed, revealing that a knowledge-retention need is not necessarily tied to one technological practice.
+Additional Assumptions:
+- TK05 with TP Convergence &lt;TP03;TP09;TP10;TP12&gt;
+- TK05 with TP Divergence &lt;TP01;TP04;TP06;TP07;TP13;TP16&gt;
+***Input data***
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+WHERE tk.node_id = 'h001M01TK05' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, COLLECT({src_node:tk, rel: r, dst_node: b}) AS tpBy,
+COLLECT(DISTINCT b) AS tp_list
+OPTIONAL MATCH (tp)-[r]-(b:EnvironmentalDependency|Limitation|OrganizationalDependency) 
+WHERE tp in tp_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy, tp_list, 
+COLLECT({src_node:tp, rel: r, dst_node: b}) AS depBy,
+COLLECT(DISTINCT b) AS dep_list
+OPTIONAL MATCH (tk)-[r:is_an_instance_of]-(b)
+WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy,tp_list,depBy,dep_list,
+COLLECT({src_node:tk, rel: r, dst_node: b}) AS tk_child_By,
+COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in tp_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy, tk_child_By,depBy,dep_list,tp_list,tk_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_child_by,
+COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in dep_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH tk, tpBy, tk_child_By,depBy,dep_list,tp_list,tk_child_list,tp_child_by,tp_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_child_by,
+COLLECT(DISTINCT b) AS dep_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in tk_child_list
+WITH tk, tpBy, tk_child_By,tp_child_by,dep_child_by,dep_child_list,depBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS childBy,
+COLLECT(DISTINCT a) AS tp_child_list,
+COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in tp_child_list AND b in dep_child_list
+WITH tk, tpBy, tk_child_By,tp_child_by,dep_child_by,childBy,depBy,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_childBy
+RETURN tk, tpBy,tk_child_By,tp_child_by,childBy,dep_childBy,depBy</t>
+  </si>
+  <si>
+    <t>Transfer Preposition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
+***Task***
+Analyze the knowledge graphs extracted from multiple cases and conduct the transfer proposition analysis to answer such questions 
+How Health Services Inspires Manufacturing？ introduce 1-2 patterns in 200 words
+How Manufacturing Inspires Construction？ introduce 1-2 patterns in 200 words
+How Construction Inspires Health Services？introduce 1-2 patterns in 200 words
+The candidate patterns：
+&lt;TP01, TK06&gt;
+&lt;TP03, TK07&gt;
+&lt;TP03, TK08&gt;
+&lt;TP03, TK10&gt;
+&lt;TP07, TK10&gt;
+&lt;TP08, TK12&gt;
+&lt;TP09, TK05&gt;
+&lt;TP10, TK04&gt;
+&lt;TP10, TK05&gt;
+&lt;TP11, TK04&gt;
+&lt;TP12, TK05&gt;
+&lt;TP13, TK10&gt;
+***Input data***
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+MATCH (a:TacitKnowledge|TechnologyenablePractice|TraditionalHumancentralPractice|EnvironmentalDependency|OrganizationalDependency|Limitation)-[r]-(b:TacitKnowledge|TechnologyenablePractice|TraditionalHumancentralPractice|EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE NOT coalesce(a.node_name, '') STARTS WITH 'Ambiguous' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH COLLECT({src_node:a, rel: r, dst_node: b}) AS a_b_By,
+COLLECT(DISTINCT a) AS a_list,
+COLLECT(DISTINCT b) AS b_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a IN a_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH a_b_By, a_list, b_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS a_child_By,
+COLLECT(DISTINCT b) AS a_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a IN b_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH a_b_By, a_list, b_list,a_child_By,a_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS b_child_By,
+COLLECT(DISTINCT b) AS b_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in a_child_list AND b in b_child_list
+WITH a_b_By, a_child_By,a_child_list,b_child_By,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS a_b_childBy
+RETURN a_b_By, a_child_By,a_child_list,b_child_By,a_b_childBy
+***Output Structure***
+How Health Services Inspires Manufacturing
+How Manufacturing Inspires Construction
+How Construction Inspires Health Services
+</t>
+  </si>
+  <si>
+    <t>Configuration Variation</t>
+  </si>
+  <si>
+    <t>MATCH (a:TacitKnowledge|TechnologyenablePractice|TraditionalHumancentralPractice|EnvironmentalDependency|OrganizationalDependency|Limitation)-[r]-(b:TacitKnowledge|TechnologyenablePractice|TraditionalHumancentralPractice|EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE NOT coalesce(a.node_name, '') STARTS WITH 'Ambiguous' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH COLLECT({src_node:a, rel: r, dst_node: b}) AS a_b_By,
+COLLECT(DISTINCT a) AS a_list,
+COLLECT(DISTINCT b) AS b_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a IN a_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH a_b_By, a_list, b_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS a_child_By,
+COLLECT(DISTINCT b) AS a_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a IN b_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH a_b_By, a_list, b_list,a_child_By,a_child_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS b_child_By,
+COLLECT(DISTINCT b) AS b_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in a_child_list AND b in b_child_list
+WITH a_b_By, a_child_By,a_child_list,b_child_By,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS a_b_childBy
+RETURN a_b_By, a_child_By,a_child_list,b_child_By,a_b_childBy</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Recommended name</t>
+  </si>
+  <si>
+    <t>⟨TP03, TK05⟩</t>
+  </si>
+  <si>
+    <t>XR-Mediated Embodied Skill Capture and Assessment</t>
+  </si>
+  <si>
+    <t>⟨TP03, TK06⟩</t>
+  </si>
+  <si>
+    <t>XR-Situated Perceptual Recognition Convergence</t>
+  </si>
+  <si>
+    <t>⟨TP06, TK06⟩</t>
+  </si>
+  <si>
+    <t>Sensor-Based Perceptual Expertise Capture</t>
+  </si>
+  <si>
+    <t>⟨TP06, TK07⟩</t>
+  </si>
+  <si>
+    <t>Wearable Capture of Postural and Spatial Control</t>
+  </si>
+  <si>
+    <t>⟨TP07, TK06⟩</t>
+  </si>
+  <si>
+    <t>Algorithmic Extraction of Perceptual Expertise</t>
+  </si>
+  <si>
+    <t>⟨TP01, TK06⟩</t>
+  </si>
+  <si>
+    <t>Model-Based Spatial Recognition and Assessment</t>
+  </si>
+  <si>
+    <t>⟨TP03, TK07⟩</t>
+  </si>
+  <si>
+    <t>XR Capture of Embodied Spatial Control</t>
+  </si>
+  <si>
+    <t>⟨TP03, TK08⟩</t>
+  </si>
+  <si>
+    <t>XR-Rehearsed Rapid Hazard Response</t>
+  </si>
+  <si>
+    <t>⟨TP03, TK10⟩</t>
+  </si>
+  <si>
+    <t>XR-Mediated Professional Judgment Calibration</t>
+  </si>
+  <si>
+    <t>⟨TP07, TK10⟩</t>
+  </si>
+  <si>
+    <t>Algorithmic Codification of Professional Judgment</t>
+  </si>
+  <si>
+    <t>⟨TP08, TK12⟩</t>
+  </si>
+  <si>
+    <t>Generative Transfer of Organizational Practice</t>
+  </si>
+  <si>
+    <t>⟨TP09, TK05⟩</t>
+  </si>
+  <si>
+    <t>Semantic Representation of Embodied Craft Skill</t>
+  </si>
+  <si>
+    <t>⟨TP10, TK04⟩</t>
+  </si>
+  <si>
+    <t>Archival Capture of Unarticulated Expertise</t>
+  </si>
+  <si>
+    <t>⟨TP10, TK05⟩</t>
+  </si>
+  <si>
+    <t>Archival Codification of Embodied Craft Skill</t>
+  </si>
+  <si>
+    <t>⟨TP11, TK04⟩</t>
+  </si>
+  <si>
+    <t>Collaborative Articulation of Unrecognized Know-how</t>
+  </si>
+  <si>
+    <t>⟨TP12, TK05⟩</t>
+  </si>
+  <si>
+    <t>Blended Internalization of Embodied Skill</t>
+  </si>
+  <si>
+    <t>⟨TP13, TK10⟩</t>
+  </si>
+  <si>
+    <t>Criteria-Based Evaluation of Professional Judgment</t>
+  </si>
 </sst>
 </file>
 
@@ -1462,7 +1996,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1474,6 +2008,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF545454"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1965,147 +2506,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2135,7 +2679,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2684,119 +3228,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="26.953125" customWidth="1"/>
-    <col min="3" max="3" width="45.046875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="31.546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="45.046875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31.546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.6484375" customWidth="1"/>
     <col min="7" max="7" width="44.65625" customWidth="1"/>
+    <col min="9" max="9" width="14.703125" customWidth="1"/>
+    <col min="10" max="10" width="21.2890625" customWidth="1"/>
+    <col min="11" max="11" width="22.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1" spans="1:8">
-      <c r="A1" s="19" t="s">
+    <row r="1" s="19" customFormat="1" spans="1:11">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="84" spans="1:8">
-      <c r="A2" s="16" t="s">
+    <row r="2" ht="84" spans="1:11">
+      <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="str" cm="1">
+      <c r="E2" s="8" t="str" cm="1">
         <f t="array" ref="E2">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A2,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="F2" s="7" t="str" cm="1">
+      <c r="F2" s="8" t="str" cm="1">
         <f t="array" ref="F2">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A2,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G2" s="7" t="str" cm="1">
+      <c r="G2" s="8" t="str" cm="1">
         <f t="array" ref="G2">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A2,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="15">
         <f>3-COUNTIF(E2:G2,"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="3" ht="51" spans="1:8">
-      <c r="A3" s="16" t="s">
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="16" t="s">
+    </row>
+    <row r="3" ht="51" spans="1:11">
+      <c r="A3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="B3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="str" cm="1">
+      <c r="E3" s="8" t="str" cm="1">
         <f t="array" ref="E3">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A3,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F3" s="7" t="str" cm="1">
+      <c r="F3" s="8" t="str" cm="1">
         <f t="array" ref="F3">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A3,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="str" cm="1">
+      <c r="G3" s="8" t="str" cm="1">
         <f t="array" ref="G3">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A3,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="15">
         <f t="shared" ref="H3:H16" si="0">3-COUNTIF(E3:G3,"")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="152" spans="1:8">
-      <c r="A4" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="16" t="s">
+    <row r="4" ht="152" spans="1:11">
+      <c r="A4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="7" t="str" cm="1">
+      <c r="C4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="8" t="str" cm="1">
         <f t="array" ref="E4">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A4,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
@@ -2804,14 +3357,14 @@
 TK08 Immediate Embodied Response to Changing Conditions
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F4" s="7" t="str" cm="1">
+      <c r="F4" s="8" t="str" cm="1">
         <f t="array" ref="F4">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A4,s002_insights!A:A,0)),"")</f>
-        <v>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+        <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="G4" s="7" t="str" cm="1">
+      <c r="G4" s="8" t="str" cm="1">
         <f t="array" ref="G4">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A4,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
@@ -2819,398 +3372,442 @@
 TK11 Informal Coordination, Communication, and Escalation Know-how
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" ht="68" spans="1:8">
-      <c r="A5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="68" spans="1:11">
+      <c r="A5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="7" t="str" cm="1">
+      <c r="E5" s="8" t="str" cm="1">
         <f t="array" ref="E5">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A5,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F5" s="7" t="str" cm="1">
+      <c r="F5" s="8" t="str" cm="1">
         <f t="array" ref="F5">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A5,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="G5" s="7" t="str" cm="1">
+      <c r="G5" s="8" t="str" cm="1">
         <f t="array" ref="G5">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A5,s003_insights!A:A,0)),"")</f>
         <v>TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="51" spans="1:8">
-      <c r="A6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="16" t="s">
+    <row r="6" ht="51" spans="1:11">
+      <c r="A6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="7" t="str" cm="1">
+      <c r="E6" s="8" t="str" cm="1">
         <f t="array" ref="E6">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A6,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="7" t="str" cm="1">
+      <c r="F6" s="8" t="str" cm="1">
         <f t="array" ref="F6">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A6,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="str" cm="1">
+      <c r="G6" s="8" t="str" cm="1">
         <f t="array" ref="G6">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A6,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="101" spans="1:8">
-      <c r="A7" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="16" t="s">
+    <row r="7" ht="152" spans="1:11">
+      <c r="A7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="7" t="str" cm="1">
+      <c r="E7" s="8" t="str" cm="1">
         <f t="array" ref="E7">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A7,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="F7" s="7" t="str" cm="1">
+      <c r="F7" s="8" t="str" cm="1">
         <f t="array" ref="F7">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A7,s002_insights!A:A,0)),"")</f>
-        <v>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+        <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="G7" s="7" t="str" cm="1">
+      <c r="G7" s="8" t="str" cm="1">
         <f t="array" ref="G7">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A7,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="8" ht="101" spans="1:8">
-      <c r="A8" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="I7" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" ht="168" spans="1:11">
+      <c r="A8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="7" t="str" cm="1">
+      <c r="E8" s="8" t="str" cm="1">
         <f t="array" ref="E8">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A8,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F8" s="7" t="str" cm="1">
+      <c r="F8" s="8" t="str" cm="1">
         <f t="array" ref="F8">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A8,s002_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
-TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="G8" s="7" t="str" cm="1">
+      <c r="G8" s="8" t="str" cm="1">
         <f t="array" ref="G8">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A8,s003_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="9" ht="84" spans="1:8">
-      <c r="A9" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="16" t="s">
+      <c r="I8" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="101" spans="1:11">
+      <c r="A9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="7" t="str" cm="1">
+      <c r="E9" s="8" t="str" cm="1">
         <f t="array" ref="E9">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A9,s001_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="F9" s="7" t="str" cm="1">
+      <c r="F9" s="8" t="str" cm="1">
         <f t="array" ref="F9">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A9,s002_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G9" s="7" t="str" cm="1">
+      <c r="G9" s="8" t="str" cm="1">
         <f t="array" ref="G9">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A9,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="10" ht="118" spans="1:8">
-      <c r="A10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="I9" s="17"/>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="118" spans="1:11">
+      <c r="A10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="7" t="str" cm="1">
+      <c r="E10" s="8" t="str" cm="1">
         <f t="array" ref="E10">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A10,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="F10" s="7" t="str" cm="1">
+      <c r="F10" s="8" t="str" cm="1">
         <f t="array" ref="F10">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A10,s002_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G10" s="7" t="str" cm="1">
+      <c r="G10" s="8" t="str" cm="1">
         <f t="array" ref="G10">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A10,s003_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment
 TK09 Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="11" ht="185" spans="1:8">
-      <c r="A11" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="16" t="s">
+      <c r="I10" s="17"/>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="219" spans="1:11">
+      <c r="A11" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="7" t="str" cm="1">
+      <c r="E11" s="8" t="str" cm="1">
         <f t="array" ref="E11">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A11,s001_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
-TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment
 TK11 Informal Coordination, Communication, and Escalation Know-how
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="F11" s="7" t="str" cm="1">
+      <c r="F11" s="8" t="str" cm="1">
         <f t="array" ref="F11">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A11,s002_insights!A:A,0)),"")</f>
-        <v>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+        <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="G11" s="7" t="str" cm="1">
+      <c r="G11" s="8" t="str" cm="1">
         <f t="array" ref="G11">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A11,s003_insights!A:A,0)),"")</f>
         <v>TK09 Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="12" ht="101" spans="1:8">
-      <c r="A12" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="7" t="str" cm="1">
+      <c r="I11" s="17"/>
+      <c r="J11" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" ht="135" spans="1:11">
+      <c r="A12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="8" t="str" cm="1">
         <f t="array" ref="E12">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A12,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="7" t="str" cm="1">
+      <c r="F12" s="8" t="str" cm="1">
         <f t="array" ref="F12">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A12,s002_insights!A:A,0)),"")</f>
-        <v>TK04 TK04 Unrecognized or Unarticulated Personal Know-how
+        <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK09 Shared Professional Language and Contextual Meaning
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G12" s="7" t="str" cm="1">
+      <c r="G12" s="8" t="str" cm="1">
         <f t="array" ref="G12">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A12,s003_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="13" ht="68" spans="1:8">
-      <c r="A13" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="7" t="str" cm="1">
+      <c r="I12" s="17"/>
+      <c r="J12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" ht="84" spans="1:11">
+      <c r="A13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="8" t="str" cm="1">
         <f t="array" ref="E13">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A13,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK11 Informal Coordination, Communication, and Escalation Know-how</v>
       </c>
-      <c r="F13" s="7" t="str" cm="1">
+      <c r="F13" s="8" t="str" cm="1">
         <f t="array" ref="F13">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A13,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="G13" s="7" t="str" cm="1">
+      <c r="G13" s="8" t="str" cm="1">
         <f t="array" ref="G13">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A13,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="14" ht="51" spans="1:8">
-      <c r="A14" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="16" t="s">
+      <c r="I13" s="17"/>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="84" spans="1:11">
+      <c r="A14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="7" t="str" cm="1">
+      <c r="E14" s="8" t="str" cm="1">
         <f t="array" ref="E14">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A14,s001_insights!A:A,0)),"")</f>
         <v>TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F14" s="7" t="str" cm="1">
+      <c r="F14" s="8" t="str" cm="1">
         <f t="array" ref="F14">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A14,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="G14" s="7" t="str" cm="1">
+      <c r="G14" s="8" t="str" cm="1">
         <f t="array" ref="G14">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A14,s003_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="15">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="15" ht="84" spans="1:8">
-      <c r="A15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="16" t="s">
+      <c r="I14" s="17"/>
+      <c r="J14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" ht="84" spans="1:11">
+      <c r="A15" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="7" t="str" cm="1">
+      <c r="E15" s="8" t="str" cm="1">
         <f t="array" ref="E15">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A15,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="7" t="str" cm="1">
+      <c r="F15" s="8" t="str" cm="1">
         <f t="array" ref="F15">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A15,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="7" t="str" cm="1">
+      <c r="G15" s="8" t="str" cm="1">
         <f t="array" ref="G15">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A15,s003_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" ht="84" spans="1:8">
-      <c r="A16" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="7" t="str" cm="1">
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" ht="84" spans="1:11">
+      <c r="A16" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="8" t="str" cm="1">
         <f t="array" ref="E16">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A16,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="7" t="str" cm="1">
+      <c r="F16" s="8" t="str" cm="1">
         <f t="array" ref="F16">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A16,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="G16" s="7" t="str" cm="1">
+      <c r="G16" s="8" t="str" cm="1">
         <f t="array" ref="G16">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A16,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="I16" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3231,283 +3828,283 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" ht="51" spans="1:6">
+      <c r="A2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:6">
+      <c r="A3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" ht="51" spans="1:6">
+      <c r="A4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" ht="51" spans="1:6">
+      <c r="A5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" ht="51" spans="1:6">
+      <c r="A6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" ht="51" spans="1:6">
+      <c r="A7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" ht="51" spans="1:6">
+      <c r="A8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" ht="51" spans="1:6">
+      <c r="A9" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" ht="51" spans="1:6">
+      <c r="A10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" ht="51" spans="1:6">
+      <c r="A11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="B11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="C11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="1:6">
+      <c r="A12" s="16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" ht="51" spans="1:6">
-      <c r="A2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" ht="51" spans="1:6">
-      <c r="A3" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="D12" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:6">
+      <c r="A13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" ht="51" spans="1:6">
-      <c r="A4" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="C13" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" ht="34" spans="1:6">
+      <c r="A14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" ht="51" spans="1:6">
-      <c r="A5" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" ht="51" spans="1:6">
-      <c r="A6" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" ht="51" spans="1:6">
-      <c r="A7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" ht="51" spans="1:6">
-      <c r="A8" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" ht="51" spans="1:6">
-      <c r="A9" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="51" spans="1:6">
-      <c r="A10" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" ht="51" spans="1:6">
-      <c r="A11" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" ht="51" spans="1:6">
-      <c r="A12" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" ht="51" spans="1:6">
-      <c r="A13" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" ht="34" spans="1:6">
-      <c r="A14" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>81</v>
+      <c r="D14" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3522,332 +4119,332 @@
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="15.4921875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="24.734375" style="9" customWidth="1"/>
-    <col min="3" max="4" width="30.7265625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="35.6796875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="48.953125" style="9" customWidth="1"/>
-    <col min="7" max="7" width="45.5703125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="15.4921875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="24.734375" style="10" customWidth="1"/>
+    <col min="3" max="4" width="30.7265625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="35.6796875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="48.953125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="45.5703125" style="10" customWidth="1"/>
     <col min="9" max="9" width="26.6015625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:9">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="D1" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="84" spans="1:9">
-      <c r="A2" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="14">
+      <c r="A2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="15">
         <f>3-COUNTIF(E2:G2,"")</f>
         <v>2</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>66</v>
+      <c r="I2" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="152" customHeight="1" spans="1:9">
-      <c r="A3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="14">
+      <c r="A3" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="15">
         <f>3-COUNTIF(E3:G3,"")</f>
         <v>3</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>64</v>
+      <c r="I3" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" ht="185" spans="1:9">
-      <c r="A4" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="14">
+      <c r="A4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4" s="15">
         <f>3-COUNTIF(E4:G4,"")</f>
         <v>3</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>64</v>
+      <c r="I4" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="135" spans="1:9">
-      <c r="A5" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="14">
+      <c r="A5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="15">
         <f>3-COUNTIF(E5:G5,"")</f>
         <v>3</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>64</v>
+      <c r="I5" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="101" spans="1:9">
-      <c r="A6" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F6" s="12" t="s">
+      <c r="A6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14">
+      <c r="E6" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="15">
         <f>3-COUNTIF(E6:G6,"")</f>
         <v>2</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>68</v>
+      <c r="I6" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="68" spans="1:9">
-      <c r="A7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H7" s="14">
+      <c r="A7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="H7" s="15">
         <f>3-COUNTIF(E7:G7,"")</f>
         <v>2</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>61</v>
+      <c r="I7" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" ht="152" customHeight="1" spans="1:9">
-      <c r="A8" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="14">
+      <c r="A8" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="H8" s="15">
         <f>3-COUNTIF(E8:G8,"")</f>
         <v>2</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>66</v>
+      <c r="I8" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" ht="168" spans="1:9">
-      <c r="A9" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" s="14">
+      <c r="A9" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H9" s="15">
         <f>3-COUNTIF(E9:G9,"")</f>
         <v>3</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>64</v>
+      <c r="I9" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10" ht="84" spans="1:9">
-      <c r="A10" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="14">
+      <c r="H10" s="15">
         <f>3-COUNTIF(E10:G10,"")</f>
         <v>2</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>61</v>
+      <c r="I10" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" ht="84" spans="1:9">
-      <c r="A11" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="H11" s="14">
+      <c r="E11" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="15">
         <f>3-COUNTIF(E11:G11,"")</f>
         <v>3</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>64</v>
+      <c r="I11" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="152" customHeight="1"/>
@@ -3868,282 +4465,282 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="25.3046875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.0546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="25.3046875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.0546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.09375" customWidth="1"/>
     <col min="5" max="5" width="41.671875" customWidth="1"/>
-    <col min="6" max="6" width="45.9375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="45.9375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>59</v>
+      <c r="C1" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:6">
-      <c r="A2" s="7" t="str">
+      <c r="A2" s="8" t="str">
         <f>cross_sector_insights_tk!A2</f>
         <v>TK02</v>
       </c>
-      <c r="B2" s="7" t="str">
+      <c r="B2" s="8" t="str">
         <f>cross_sector_insights_tk!B2</f>
         <v>Knowledge Conveyed Through Examples or Demonstration</v>
       </c>
-      <c r="C2" s="7" t="str">
+      <c r="C2" s="8" t="str">
         <f>cross_sector_insights_tk!D2</f>
         <v>Relational Tacit Knowledge</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="9" t="str">
         <f>cross_sector_insights_tk!H2&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E2" s="8" t="str">
+      <c r="E2" s="9" t="str">
         <f>cross_sector_insights_tk!I2</f>
         <v>Manufacturing; Health Services</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>142</v>
+      <c r="F2" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:6">
-      <c r="A3" s="7" t="str">
+      <c r="A3" s="8" t="str">
         <f>cross_sector_insights_tk!A3</f>
         <v>TK04</v>
       </c>
-      <c r="B3" s="7" t="str">
+      <c r="B3" s="8" t="str">
         <f>cross_sector_insights_tk!B3</f>
         <v>Unrecognized or Unarticulated Personal Know-how</v>
       </c>
-      <c r="C3" s="7" t="str">
+      <c r="C3" s="8" t="str">
         <f>cross_sector_insights_tk!D3</f>
         <v>Relational Tacit Knowledge</v>
       </c>
-      <c r="D3" s="8" t="str">
+      <c r="D3" s="9" t="str">
         <f>cross_sector_insights_tk!H3&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E3" s="8" t="str">
+      <c r="E3" s="9" t="str">
         <f>cross_sector_insights_tk!I3</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>143</v>
+      <c r="F3" s="8" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:6">
-      <c r="A4" s="7" t="str">
+      <c r="A4" s="8" t="str">
         <f>cross_sector_insights_tk!A4</f>
         <v>TK05</v>
       </c>
-      <c r="B4" s="7" t="str">
+      <c r="B4" s="8" t="str">
         <f>cross_sector_insights_tk!B4</f>
         <v>Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="C4" s="7" t="str">
+      <c r="C4" s="8" t="str">
         <f>cross_sector_insights_tk!D4</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D4" s="8" t="str">
+      <c r="D4" s="9" t="str">
         <f>cross_sector_insights_tk!H4&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E4" s="8" t="str">
+      <c r="E4" s="9" t="str">
         <f>cross_sector_insights_tk!I4</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>144</v>
+      <c r="F4" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:6">
-      <c r="A5" s="7" t="str">
+      <c r="A5" s="8" t="str">
         <f>cross_sector_insights_tk!A5</f>
         <v>TK06</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="8" t="str">
         <f>cross_sector_insights_tk!B5</f>
         <v>Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="8" t="str">
         <f>cross_sector_insights_tk!D5</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="9" t="str">
         <f>cross_sector_insights_tk!H5&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E5" s="8" t="str">
+      <c r="E5" s="9" t="str">
         <f>cross_sector_insights_tk!I5</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>145</v>
+      <c r="F5" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:6">
-      <c r="A6" s="7" t="str">
+      <c r="A6" s="8" t="str">
         <f>cross_sector_insights_tk!A6</f>
         <v>TK07</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="8" t="str">
         <f>cross_sector_insights_tk!B6</f>
         <v>Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="C6" s="7" t="str">
+      <c r="C6" s="8" t="str">
         <f>cross_sector_insights_tk!D6</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="9" t="str">
         <f>cross_sector_insights_tk!H6&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E6" s="8" t="str">
+      <c r="E6" s="9" t="str">
         <f>cross_sector_insights_tk!I6</f>
         <v>Construction; Manufacturing</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>146</v>
+      <c r="F6" s="8" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="7" ht="51" spans="1:6">
-      <c r="A7" s="7" t="str">
+      <c r="A7" s="8" t="str">
         <f>cross_sector_insights_tk!A7</f>
         <v>TK08</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="8" t="str">
         <f>cross_sector_insights_tk!B7</f>
         <v>Immediate Embodied Response to Changing Conditions</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="8" t="str">
         <f>cross_sector_insights_tk!D7</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D7" s="8" t="str">
+      <c r="D7" s="9" t="str">
         <f>cross_sector_insights_tk!H7&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E7" s="8" t="str">
+      <c r="E7" s="9" t="str">
         <f>cross_sector_insights_tk!I7</f>
         <v>Construction; Health Services</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>147</v>
+      <c r="F7" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:6">
-      <c r="A8" s="7" t="str">
+      <c r="A8" s="8" t="str">
         <f>cross_sector_insights_tk!A8</f>
         <v>TK09</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="8" t="str">
         <f>cross_sector_insights_tk!B8</f>
         <v>Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="8" t="str">
         <f>cross_sector_insights_tk!D8</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D8" s="8" t="str">
+      <c r="D8" s="9" t="str">
         <f>cross_sector_insights_tk!H8&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="9" t="str">
         <f>cross_sector_insights_tk!I8</f>
         <v>Manufacturing; Health Services</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>148</v>
+      <c r="F8" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="7" t="str">
+      <c r="A9" s="8" t="str">
         <f>cross_sector_insights_tk!A9</f>
         <v>TK10</v>
       </c>
-      <c r="B9" s="7" t="str">
+      <c r="B9" s="8" t="str">
         <f>cross_sector_insights_tk!B9</f>
         <v>Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="C9" s="7" t="str">
+      <c r="C9" s="8" t="str">
         <f>cross_sector_insights_tk!D9</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D9" s="8" t="str">
+      <c r="D9" s="9" t="str">
         <f>cross_sector_insights_tk!H9&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E9" s="8" t="str">
+      <c r="E9" s="9" t="str">
         <f>cross_sector_insights_tk!I9</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>149</v>
+      <c r="F9" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="10" ht="51" spans="1:6">
-      <c r="A10" s="7" t="str">
+      <c r="A10" s="8" t="str">
         <f>cross_sector_insights_tk!A10</f>
         <v>TK11</v>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="8" t="str">
         <f>cross_sector_insights_tk!B10</f>
         <v>Informal Coordination, Communication, and Escalation Know-how</v>
       </c>
-      <c r="C10" s="7" t="str">
+      <c r="C10" s="8" t="str">
         <f>cross_sector_insights_tk!D10</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D10" s="8" t="str">
+      <c r="D10" s="9" t="str">
         <f>cross_sector_insights_tk!H10&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E10" s="8" t="str">
+      <c r="E10" s="9" t="str">
         <f>cross_sector_insights_tk!I10</f>
         <v>Construction; Health Services</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>150</v>
+      <c r="F10" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="7" t="str">
+      <c r="A11" s="8" t="str">
         <f>cross_sector_insights_tk!A11</f>
         <v>TK12</v>
       </c>
-      <c r="B11" s="7" t="str">
+      <c r="B11" s="8" t="str">
         <f>cross_sector_insights_tk!B11</f>
         <v>Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="C11" s="7" t="str">
+      <c r="C11" s="8" t="str">
         <f>cross_sector_insights_tk!D11</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D11" s="8" t="str">
+      <c r="D11" s="9" t="str">
         <f>cross_sector_insights_tk!H11&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E11" s="8" t="str">
+      <c r="E11" s="9" t="str">
         <f>cross_sector_insights_tk!I11</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>151</v>
+      <c r="F11" s="8" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4158,266 +4755,266 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="25.515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="34.765625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="23.171875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="33.8515625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="32.9375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="23.0390625" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.4375" style="4"/>
+    <col min="1" max="1" width="12.109375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="25.515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="34.765625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23.171875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="33.8515625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="32.9375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="23.0390625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.4375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="17" spans="1:8">
-      <c r="A1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A3" s="4" t="s">
+    <row r="1" s="5" customFormat="1" ht="17" spans="1:8">
+      <c r="A1" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B1" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A4" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="2" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A4" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A5" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A5" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A6" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A6" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A7" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E6" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A7" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A8" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E7" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A9" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E8" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A9" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A10" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E9" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" s="5" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A10" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" s="4" customFormat="1" spans="1:8">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" s="4" customFormat="1" spans="1:8">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="E10" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" s="5" customFormat="1" spans="1:8">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" s="5" customFormat="1" spans="1:8">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4431,294 +5028,294 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.0078125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="24.8671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="27.8671875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="26.0390625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="41.1484375" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.4375" style="4"/>
+    <col min="1" max="1" width="16.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.0078125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.8671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="27.8671875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="26.0390625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="41.1484375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.4375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:7">
-      <c r="A1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A2" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="4" t="s">
+    <row r="1" s="5" customFormat="1" spans="1:7">
+      <c r="A1" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A2" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A5" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A5" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A6" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A7" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="G7" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A8" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="E9" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A10" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" s="5" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A12" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A9" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A10" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A11" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A12" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>256</v>
+      <c r="G12" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="6:6">
-      <c r="F19" s="4" t="s">
-        <v>257</v>
+      <c r="F19" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -4742,255 +5339,255 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="F1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:7">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>259</v>
+        <v>174</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="G2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:7">
       <c r="A3" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>264</v>
+        <v>174</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="G3" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" ht="409.5" spans="1:7">
       <c r="A4" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>268</v>
+        <v>174</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>270</v>
+        <v>283</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" ht="409.5" spans="1:7">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>273</v>
+        <v>174</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="F5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:7">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>277</v>
+        <v>174</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>279</v>
+        <v>292</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="G6" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:7">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>282</v>
+        <v>174</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>184</v>
+        <v>297</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="G7" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" ht="409.5" spans="1:7">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>286</v>
+        <v>174</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>288</v>
+        <v>301</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="G8" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:7">
       <c r="A9" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>291</v>
+        <v>174</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="F9" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="G9" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" ht="409.5" spans="1:7">
       <c r="A10" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>296</v>
+        <v>174</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F10" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="G10" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" ht="409.5" spans="1:7">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>300</v>
+        <v>174</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="F11" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="G11" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -5002,56 +5599,271 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="15.890625" customWidth="1"/>
+    <col min="1" max="1" width="27.6875" customWidth="1"/>
     <col min="2" max="2" width="33.7265625" customWidth="1"/>
     <col min="3" max="3" width="46.21875" customWidth="1"/>
+    <col min="4" max="4" width="73.78125" customWidth="1"/>
+    <col min="5" max="5" width="50.5234375" customWidth="1"/>
+    <col min="6" max="6" width="16.7421875" customWidth="1"/>
+    <col min="7" max="7" width="70.4765625" customWidth="1"/>
+    <col min="8" max="8" width="79.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="2" ht="68" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>307</v>
+    <row r="1" ht="21" customHeight="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" ht="409.5" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:8">
+      <c r="A4" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" ht="409.5" spans="1:8">
+      <c r="A5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" ht="409.5" spans="1:8">
+      <c r="A6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="17.578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="55.3359375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="3" ht="84" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" ht="17" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" ht="68" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>313</v>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" ht="17" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="6" ht="17" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" ht="17" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" ht="17" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" ht="17" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="16" ht="17" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17" ht="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/src/conf/cross_sector_insight/cross_sector_insights.xlsx
+++ b/src/conf/cross_sector_insight/cross_sector_insights.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11060" firstSheet="3" activeTab="8"/>
+    <workbookView windowWidth="28800" windowHeight="11240" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="cross_sector_insights_tp" sheetId="4" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="s002_insights" sheetId="2" r:id="rId6"/>
     <sheet name="s003_insights" sheetId="1" r:id="rId7"/>
     <sheet name="pattern type" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet10" sheetId="10" r:id="rId9"/>
+    <sheet name="potenial patterns" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cross_sector_insights_tp!$A$1:$H$16</definedName>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="396">
   <si>
     <t>ID</t>
   </si>
@@ -291,6 +291,9 @@
     <t>Potential Pattern</t>
   </si>
   <si>
+    <t>Potential Patterns</t>
+  </si>
+  <si>
     <t>2/3</t>
   </si>
   <si>
@@ -301,6 +304,9 @@
 TK Divergence: TK05; TK10</t>
   </si>
   <si>
+    <t>Perceptual convergence with health-specific extension to motor skill and professional judgment</t>
+  </si>
+  <si>
     <t>3/3</t>
   </si>
   <si>
@@ -311,6 +317,9 @@
 TK Divergence: TK04; TK11</t>
   </si>
   <si>
+    <t>Strong embodied–perceptual convergence with sector-specific extensions of situated know-how</t>
+  </si>
+  <si>
     <t>Manufacturing; Health Services</t>
   </si>
   <si>
@@ -318,6 +327,9 @@
 TK Divergence: TK05; TK10</t>
   </si>
   <si>
+    <t>Sector-divergent experiential feedback targeting motor skill and professional judgment</t>
+  </si>
+  <si>
     <t>Construction; Manufacturing</t>
   </si>
   <si>
@@ -325,34 +337,98 @@
 TK Divergence: TK04; TK05</t>
   </si>
   <si>
+    <t>Embodied–perceptual convergence with broader know-how capture in manufacturing</t>
+  </si>
+  <si>
     <t>TK Convergence: TK06; TK10 
 TK Divergence: TK02; TK04; TK05</t>
   </si>
   <si>
+    <t>Perceptual convergence with sector-specific extensions to judgment, demonstration, motor skill, and unarticulated know-how</t>
+  </si>
+  <si>
     <t>TK Convergence: TK12 
 TK Divergence: TK06; TK07</t>
   </si>
   <si>
+    <t>Organizational-practice convergence with manufacturing extension to embodied–perceptual knowledge</t>
+  </si>
+  <si>
     <t>TK Convergence: TK05 
 TK Divergence: TK02; TK09; TK10; TK12</t>
   </si>
   <si>
+    <r>
+      <t>cross-industry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>recurrence with divergent knowledge targets</t>
+    </r>
+  </si>
+  <si>
     <t>TK Convergence: TK04; TK05 
 TK Divergence: TK02; TK09; TK10; TK11; TK12</t>
   </si>
   <si>
+    <r>
+      <t>cross-industry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>recurrence with strongly sector-divergent archival knowledge targets</t>
+    </r>
+  </si>
+  <si>
     <t>TK Convergence: TK04 
 TK Divergence: TK02; TK09; TK10; TK12</t>
   </si>
   <si>
+    <t>Interpersonal and socially embedded know-how convergence with sector-specific professional and organizational extensions</t>
+  </si>
+  <si>
     <t>TK Convergence: TK05 
 TK Divergence: TK10; TK11</t>
   </si>
   <si>
+    <t>Strong motor-skill convergence with sector-specific social and professional extensions</t>
+  </si>
+  <si>
     <t>TK Convergence: TK10 
 TK Divergence: TK05; TK12</t>
   </si>
   <si>
+    <t>Professional-judgment convergence with sector-specific motor and organizational extensions</t>
+  </si>
+  <si>
     <t>1/3</t>
   </si>
   <si>
@@ -363,11 +439,17 @@
 TK Divergence: TK04</t>
   </si>
   <si>
+    <t>Unarticulated personal know-how</t>
+  </si>
+  <si>
     <t>Manufacturing</t>
   </si>
   <si>
     <t>TK Convergence: None identified 
 TK Divergence: TK05; TK06</t>
+  </si>
+  <si>
+    <t>Embodied–perceptual learning pattern</t>
   </si>
   <si>
     <t>Collins TK Taxonomy</t>
@@ -1416,6 +1498,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Identifies the strongest evidence of a </t>
     </r>
     <r>
@@ -1544,7 +1633,7 @@
   <si>
     <t xml:space="preserve">You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
 ***Task***
-Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that &lt;TP03, TK06&gt; belongs to this pattern type.
+Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that &lt;TP03, TK06&gt; belongs to this pattern type.  During the analytical process, all claims you generate should be supported by the evidence in the knowledge graphs.
 - Name: Cross-sector TP–TK convergence
 - Definition:  A comparable TP is associated with comparable TK forms across all three sectors. 
 - Purpose: Identifies the strongest evidence of a cross-sector common retention configuration and helps reveal what may transcend sector boundaries at both the practice and knowledge-target levels.
@@ -1591,8 +1680,9 @@
 Pattern Name: &lt;TP03, TK06&gt;  &lt;please name it&gt;
 Pattern Type: Cross-sector TP–TK convergence
 Technology-enable Practice Definition: Uses technologies like VR, AR, MR, CAVE, or hybrid XR environments to support embodied rehearsal, contextual guidance, historical interpretation, hazard recognition, and situated knowledge transfer.
+Quality Assessment: &lt;please assess the pattern in 100 word&gt;
 Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP03 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node&gt;  
-Inspiring Cues:
+Mechanism-based transfer considerations: &lt;Please analyze this pattern from aspects such as the basic mechanism, potential transfer scenarios, resource and environmental dependencies, organizational culture dependencies, and other limitations, and provide a 200-word explanation.&gt;
 </t>
   </si>
   <si>
@@ -1603,6 +1693,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Identifies </t>
     </r>
     <r>
@@ -1685,6 +1782,60 @@
 </t>
   </si>
   <si>
+    <t>You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
+***Task*** +Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that &lt;TP07, TK10&gt; belongs to this pattern type. During the analytical process, all claims you generate should be supported by the evidence in the knowledge graphs. +- Name: Context-bounded TP–TK convergence +- Definition: A comparable TP is associated with comparable TK forms within a sector pair or a particular sector configuration, but this convergence is not observed across all three sectors. +- Purpose: Identifies bounded commonality, showing that some retention configurations may be shared between particular contexts rather than being broadly cross-sector. This helps establish the boundary conditions of apparent generality.
+***Input data*** +Use [[$analyze-neo4j-knowledge-graph](/Users/meimei/.codex/skills/analyze-neo4j-knowledge-graph/SKILL.md)] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation)  +MATCH (tp:TechnologyenablePractice)-[r]-(tk:TacitKnowledge)  +WHERE tp.node_id = 'h001M01TP07’ AND tk.node_id = 'h001M01TK10’ +WITH tp, COLLECT({src_node:tp, rel: r, dst_node: tk}) AS tp_tk_By, +COLLECT(DISTINCT tk) AS tp_tk_list
+OPTIONAL MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation) +WHERE (a = tp OR a in tp_tk_list) AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' +WITH tp, tp_tk_By, tp_tk_list, +COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_By, +COLLECT(DISTINCT b) AS tp_r_list
+OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b) +WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' +WITH tp, tp_tk_By, tp_tk_list, tp_r_By,tp_r_list, +COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By, +COLLECT(DISTINCT b) AS tp_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b) +WHERE a in tp_tk_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' +WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list, +COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_child_by, +COLLECT(DISTINCT b) AS tk_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b) +WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' +WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list, +COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by, +COLLECT(DISTINCT b) AS tp_r_child_list
+OPTIONAL MATCH (a)-[r]-(b) +WHERE a in tp_child_list AND b in tp_r_child_list +WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, +COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_childBy
+OPTIONAL MATCH (a)-[r]-(b) +WHERE a in tk_child_list AND b in tp_r_child_list +WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,tp_r_childBy, +COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_r_childBy
+OPTIONAL MATCH (a)-[r]-(b) +WHERE a in tp_child_list AND b in tk_child_list +WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, tk_r_childBy,tp_r_childBy, +COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_tk_childBy
+RETURN tp, tp_tk_By,tp_child_By,tk_child_by,tp_r_child_by,tk_r_childBy,tp_r_childBy
+***Output Structure*** +Pattern Name: &lt;TP07, TK10&gt; &lt;please name it&gt; +Pattern Type: Context-bounded TP–TK convergence +Technology-enable Practice Definition: Uses AI, machine learning, NLP, statistical learning, or rule-based algorithms to derive classifications, forecasts, detected patterns, and predicted conditions from data.
+Quality Assessment: &lt;please assess the pattern in 100 word&gt;
+Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP07 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node, you just need keep sectors which keep relevant evidences&gt;  
+Mechanism-based transfer considerations: &lt;Please analyze this pattern from aspects such as the basic mechanism, potential transfer scenarios, resource and environmental dependencies, organizational culture dependencies, and other limitations, and provide a 200-word explanation.&gt;</t>
+  </si>
+  <si>
     <t>TK variation across TPs</t>
   </si>
   <si>
@@ -1692,6 +1843,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Identifies </t>
     </r>
     <r>
@@ -1884,6 +2042,9 @@
     <t>Recommended name</t>
   </si>
   <si>
+    <t>Pattern Type</t>
+  </si>
+  <si>
     <t>⟨TP03, TK05⟩</t>
   </si>
   <si>
@@ -1996,7 +2157,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2025,6 +2186,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman Regular"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2171,12 +2338,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2365,7 +2538,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2385,6 +2558,26 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2506,55 +2699,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2569,80 +2759,95 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2685,6 +2890,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2693,6 +2901,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3233,7 +3447,7 @@
   <cols>
     <col min="2" max="2" width="26.953125" customWidth="1"/>
     <col min="3" max="3" width="45.046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="9" customWidth="1"/>
     <col min="5" max="5" width="31.546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.6484375" customWidth="1"/>
     <col min="7" max="7" width="44.65625" customWidth="1"/>
@@ -3242,60 +3456,60 @@
     <col min="11" max="11" width="22.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="1" spans="1:11">
-      <c r="A1" s="20" t="s">
+    <row r="1" s="26" customFormat="1" spans="1:11">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="84" spans="1:11">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="8" t="str" cm="1">
+      <c r="E2" s="12" t="str" cm="1">
         <f t="array" ref="E2">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A2,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="F2" s="8" t="str" cm="1">
+      <c r="F2" s="12" t="str" cm="1">
         <f t="array" ref="F2">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A2,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G2" s="8" t="str" cm="1">
+      <c r="G2" s="12" t="str" cm="1">
         <f t="array" ref="G2">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A2,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="19">
         <f>3-COUNTIF(E2:G2,"")</f>
         <v>2</v>
       </c>
@@ -3307,49 +3521,49 @@
       </c>
     </row>
     <row r="3" ht="51" spans="1:11">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="8" t="str" cm="1">
+      <c r="E3" s="12" t="str" cm="1">
         <f t="array" ref="E3">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A3,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F3" s="8" t="str" cm="1">
+      <c r="F3" s="12" t="str" cm="1">
         <f t="array" ref="F3">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A3,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G3" s="8" t="str" cm="1">
+      <c r="G3" s="12" t="str" cm="1">
         <f t="array" ref="G3">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A3,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="19">
         <f t="shared" ref="H3:H16" si="0">3-COUNTIF(E3:G3,"")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="152" spans="1:11">
-      <c r="A4" s="17" t="s">
+    <row r="4" ht="168" spans="1:11">
+      <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="8" t="str" cm="1">
+      <c r="E4" s="12" t="str" cm="1">
         <f t="array" ref="E4">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A4,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
@@ -3357,14 +3571,14 @@
 TK08 Immediate Embodied Response to Changing Conditions
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F4" s="8" t="str" cm="1">
+      <c r="F4" s="12" t="str" cm="1">
         <f t="array" ref="F4">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A4,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="G4" s="8" t="str" cm="1">
+      <c r="G4" s="12" t="str" cm="1">
         <f t="array" ref="G4">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A4,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
@@ -3372,7 +3586,7 @@
 TK11 Informal Coordination, Communication, and Escalation Know-how
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -3387,95 +3601,95 @@
       </c>
     </row>
     <row r="5" ht="68" spans="1:11">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="8" t="str" cm="1">
+      <c r="E5" s="12" t="str" cm="1">
         <f t="array" ref="E5">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A5,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F5" s="8" t="str" cm="1">
+      <c r="F5" s="12" t="str" cm="1">
         <f t="array" ref="F5">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A5,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="G5" s="8" t="str" cm="1">
+      <c r="G5" s="12" t="str" cm="1">
         <f t="array" ref="G5">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A5,s003_insights!A:A,0)),"")</f>
         <v>TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" ht="51" spans="1:11">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="8" t="str" cm="1">
+      <c r="E6" s="12" t="str" cm="1">
         <f t="array" ref="E6">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A6,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="str" cm="1">
+      <c r="F6" s="12" t="str" cm="1">
         <f t="array" ref="F6">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A6,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G6" s="8" t="str" cm="1">
+      <c r="G6" s="12" t="str" cm="1">
         <f t="array" ref="G6">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A6,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="152" spans="1:11">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="8" t="str" cm="1">
+      <c r="E7" s="12" t="str" cm="1">
         <f t="array" ref="E7">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A7,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="F7" s="8" t="str" cm="1">
+      <c r="F7" s="12" t="str" cm="1">
         <f t="array" ref="F7">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A7,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="G7" s="8" t="str" cm="1">
+      <c r="G7" s="12" t="str" cm="1">
         <f t="array" ref="G7">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A7,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -3484,40 +3698,40 @@
       </c>
     </row>
     <row r="8" ht="168" spans="1:11">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="8" t="str" cm="1">
+      <c r="E8" s="12" t="str" cm="1">
         <f t="array" ref="E8">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A8,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F8" s="8" t="str" cm="1">
+      <c r="F8" s="12" t="str" cm="1">
         <f t="array" ref="F8">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A8,s002_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="G8" s="8" t="str" cm="1">
+      <c r="G8" s="12" t="str" cm="1">
         <f t="array" ref="G8">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A8,s003_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="22" t="s">
         <v>37</v>
       </c>
       <c r="J8" t="s">
@@ -3525,92 +3739,92 @@
       </c>
     </row>
     <row r="9" ht="101" spans="1:11">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="str" cm="1">
+      <c r="E9" s="12" t="str" cm="1">
         <f t="array" ref="E9">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A9,s001_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="F9" s="8" t="str" cm="1">
+      <c r="F9" s="12" t="str" cm="1">
         <f t="array" ref="F9">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A9,s002_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G9" s="8" t="str" cm="1">
+      <c r="G9" s="12" t="str" cm="1">
         <f t="array" ref="G9">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A9,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I9" s="17"/>
+      <c r="I9" s="22"/>
       <c r="J9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="118" spans="1:11">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="8" t="str" cm="1">
+      <c r="E10" s="12" t="str" cm="1">
         <f t="array" ref="E10">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A10,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="F10" s="8" t="str" cm="1">
+      <c r="F10" s="12" t="str" cm="1">
         <f t="array" ref="F10">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A10,s002_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G10" s="8" t="str" cm="1">
+      <c r="G10" s="12" t="str" cm="1">
         <f t="array" ref="G10">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A10,s003_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment
 TK09 Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I10" s="17"/>
+      <c r="I10" s="22"/>
       <c r="J10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="219" spans="1:11">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="8" t="str" cm="1">
+      <c r="E11" s="12" t="str" cm="1">
         <f t="array" ref="E11">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A11,s001_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
@@ -3619,195 +3833,195 @@
 TK11 Informal Coordination, Communication, and Escalation Know-how
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="F11" s="8" t="str" cm="1">
+      <c r="F11" s="12" t="str" cm="1">
         <f t="array" ref="F11">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A11,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="G11" s="8" t="str" cm="1">
+      <c r="G11" s="12" t="str" cm="1">
         <f t="array" ref="G11">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A11,s003_insights!A:A,0)),"")</f>
         <v>TK09 Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I11" s="17"/>
+      <c r="I11" s="22"/>
       <c r="J11" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" ht="135" spans="1:11">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="8" t="str" cm="1">
+      <c r="E12" s="12" t="str" cm="1">
         <f t="array" ref="E12">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A12,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="8" t="str" cm="1">
+      <c r="F12" s="12" t="str" cm="1">
         <f t="array" ref="F12">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A12,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK09 Shared Professional Language and Contextual Meaning
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G12" s="8" t="str" cm="1">
+      <c r="G12" s="12" t="str" cm="1">
         <f t="array" ref="G12">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A12,s003_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I12" s="17"/>
+      <c r="I12" s="22"/>
       <c r="J12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" ht="84" spans="1:11">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="8" t="str" cm="1">
+      <c r="E13" s="12" t="str" cm="1">
         <f t="array" ref="E13">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A13,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK11 Informal Coordination, Communication, and Escalation Know-how</v>
       </c>
-      <c r="F13" s="8" t="str" cm="1">
+      <c r="F13" s="12" t="str" cm="1">
         <f t="array" ref="F13">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A13,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="G13" s="8" t="str" cm="1">
+      <c r="G13" s="12" t="str" cm="1">
         <f t="array" ref="G13">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A13,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I13" s="17"/>
+      <c r="I13" s="22"/>
       <c r="J13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" ht="84" spans="1:11">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="8" t="str" cm="1">
+      <c r="E14" s="12" t="str" cm="1">
         <f t="array" ref="E14">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A14,s001_insights!A:A,0)),"")</f>
         <v>TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F14" s="8" t="str" cm="1">
+      <c r="F14" s="12" t="str" cm="1">
         <f t="array" ref="F14">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A14,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="G14" s="8" t="str" cm="1">
+      <c r="G14" s="12" t="str" cm="1">
         <f t="array" ref="G14">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A14,s003_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I14" s="17"/>
+      <c r="I14" s="22"/>
       <c r="J14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" ht="84" spans="1:11">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="8" t="str" cm="1">
+      <c r="E15" s="12" t="str" cm="1">
         <f t="array" ref="E15">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A15,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="8" t="str" cm="1">
+      <c r="F15" s="12" t="str" cm="1">
         <f t="array" ref="F15">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A15,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="8" t="str" cm="1">
+      <c r="G15" s="12" t="str" cm="1">
         <f t="array" ref="G15">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A15,s003_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I15" s="17"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" ht="84" spans="1:11">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="8" t="str" cm="1">
+      <c r="E16" s="12" t="str" cm="1">
         <f t="array" ref="E16">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A16,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="8" t="str" cm="1">
+      <c r="F16" s="12" t="str" cm="1">
         <f t="array" ref="F16">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A16,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="G16" s="8" t="str" cm="1">
+      <c r="G16" s="12" t="str" cm="1">
         <f t="array" ref="G16">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A16,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="19">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="17"/>
+      <c r="I16" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3818,295 +4032,339 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="3" width="24.609375" customWidth="1"/>
     <col min="4" max="4" width="20.9609375" customWidth="1"/>
     <col min="5" max="5" width="21.75" customWidth="1"/>
     <col min="6" max="6" width="37.515625" customWidth="1"/>
+    <col min="7" max="7" width="28.2734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:6">
-      <c r="A1" s="7" t="s">
+    <row r="1" ht="18.5" spans="1:7">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" ht="51" spans="1:6">
-      <c r="A2" s="16" t="s">
+      <c r="G1" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" ht="51" spans="1:7">
+      <c r="A2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="12" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="3" ht="51" spans="1:6">
-      <c r="A3" s="16" t="s">
+      <c r="F2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:7">
+      <c r="A3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="D3" s="23" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" ht="51" spans="1:6">
-      <c r="A4" s="16" t="s">
+      <c r="E3" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" ht="51" spans="1:7">
+      <c r="A4" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" ht="51" spans="1:7">
+      <c r="A5" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" ht="63" spans="1:7">
+      <c r="A6" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" ht="51" spans="1:6">
-      <c r="A5" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="F6" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" ht="63" spans="1:7">
+      <c r="A7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="D7" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" ht="51" spans="1:7">
+      <c r="A8" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" ht="51" spans="1:7">
+      <c r="A9" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" ht="78" spans="1:7">
+      <c r="A10" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="6" ht="51" spans="1:6">
-      <c r="A6" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="F10" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="51" spans="1:7">
+      <c r="A11" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" ht="63" spans="1:7">
+      <c r="A12" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" ht="51" spans="1:6">
-      <c r="A7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="D12" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:7">
+      <c r="A13" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" ht="51" spans="1:6">
-      <c r="A8" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" ht="51" spans="1:6">
-      <c r="A9" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" ht="51" spans="1:6">
-      <c r="A10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="D13" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" ht="34.75" spans="1:7">
+      <c r="A14" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" ht="51" spans="1:6">
-      <c r="A11" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" ht="51" spans="1:6">
-      <c r="A12" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" ht="51" spans="1:6">
-      <c r="A13" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" ht="34" spans="1:6">
-      <c r="A14" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
+      <c r="D14" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" ht="17.55"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4119,332 +4377,332 @@
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="15.4921875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="24.734375" style="10" customWidth="1"/>
-    <col min="3" max="4" width="30.7265625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="35.6796875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="48.953125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="45.5703125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="15.4921875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="24.734375" style="14" customWidth="1"/>
+    <col min="3" max="4" width="30.7265625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="35.6796875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="48.953125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="45.5703125" style="14" customWidth="1"/>
     <col min="9" max="9" width="26.6015625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="13" t="s">
+      <c r="D1" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" ht="84" spans="1:9">
-      <c r="A2" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="15">
-        <f>3-COUNTIF(E2:G2,"")</f>
+      <c r="A2" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="19">
+        <f t="shared" ref="H2:H11" si="0">3-COUNTIF(E2:G2,"")</f>
         <v>2</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" ht="152" customHeight="1" spans="1:9">
+      <c r="A3" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" ht="152" customHeight="1" spans="1:9">
-      <c r="A3" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="15">
-        <f>3-COUNTIF(E3:G3,"")</f>
+    <row r="4" ht="185" spans="1:9">
+      <c r="A4" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="H4" s="19">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" ht="185" spans="1:9">
-      <c r="A4" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="H4" s="15">
-        <f>3-COUNTIF(E4:G4,"")</f>
+      <c r="I4" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" ht="135" spans="1:9">
+      <c r="A5" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="19">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" ht="135" spans="1:9">
-      <c r="A5" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="15">
-        <f>3-COUNTIF(E5:G5,"")</f>
+      <c r="I5" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" ht="101" spans="1:9">
+      <c r="A6" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="16"/>
+      <c r="H6" s="19">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" ht="68" spans="1:9">
+      <c r="A7" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="19">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" ht="152" customHeight="1" spans="1:9">
+      <c r="A8" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" ht="168" spans="1:9">
+      <c r="A9" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" s="19">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" ht="101" spans="1:9">
-      <c r="A6" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="15">
-        <f>3-COUNTIF(E6:G6,"")</f>
+      <c r="I9" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" ht="84" spans="1:9">
+      <c r="A10" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="19">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" ht="68" spans="1:9">
-      <c r="A7" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="H7" s="15">
-        <f>3-COUNTIF(E7:G7,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" ht="152" customHeight="1" spans="1:9">
-      <c r="A8" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="H8" s="15">
-        <f>3-COUNTIF(E8:G8,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="I10" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" ht="84" spans="1:9">
+      <c r="A11" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="9" ht="168" spans="1:9">
-      <c r="A9" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="H9" s="15">
-        <f>3-COUNTIF(E9:G9,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" ht="84" spans="1:9">
-      <c r="A10" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="H10" s="15">
-        <f>3-COUNTIF(E10:G10,"")</f>
-        <v>2</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" ht="84" spans="1:9">
-      <c r="A11" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="H11" s="15">
-        <f>3-COUNTIF(E11:G11,"")</f>
-        <v>3</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="16" ht="152" customHeight="1"/>
@@ -4474,273 +4732,273 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:6">
-      <c r="A2" s="8" t="str">
+      <c r="A2" s="12" t="str">
         <f>cross_sector_insights_tk!A2</f>
         <v>TK02</v>
       </c>
-      <c r="B2" s="8" t="str">
+      <c r="B2" s="12" t="str">
         <f>cross_sector_insights_tk!B2</f>
         <v>Knowledge Conveyed Through Examples or Demonstration</v>
       </c>
-      <c r="C2" s="8" t="str">
+      <c r="C2" s="12" t="str">
         <f>cross_sector_insights_tk!D2</f>
         <v>Relational Tacit Knowledge</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="13" t="str">
         <f>cross_sector_insights_tk!H2&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E2" s="9" t="str">
+      <c r="E2" s="13" t="str">
         <f>cross_sector_insights_tk!I2</f>
         <v>Manufacturing; Health Services</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>156</v>
+      <c r="F2" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:6">
-      <c r="A3" s="8" t="str">
+      <c r="A3" s="12" t="str">
         <f>cross_sector_insights_tk!A3</f>
         <v>TK04</v>
       </c>
-      <c r="B3" s="8" t="str">
+      <c r="B3" s="12" t="str">
         <f>cross_sector_insights_tk!B3</f>
         <v>Unrecognized or Unarticulated Personal Know-how</v>
       </c>
-      <c r="C3" s="8" t="str">
+      <c r="C3" s="12" t="str">
         <f>cross_sector_insights_tk!D3</f>
         <v>Relational Tacit Knowledge</v>
       </c>
-      <c r="D3" s="9" t="str">
+      <c r="D3" s="13" t="str">
         <f>cross_sector_insights_tk!H3&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E3" s="9" t="str">
+      <c r="E3" s="13" t="str">
         <f>cross_sector_insights_tk!I3</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>157</v>
+      <c r="F3" s="12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:6">
-      <c r="A4" s="8" t="str">
+      <c r="A4" s="12" t="str">
         <f>cross_sector_insights_tk!A4</f>
         <v>TK05</v>
       </c>
-      <c r="B4" s="8" t="str">
+      <c r="B4" s="12" t="str">
         <f>cross_sector_insights_tk!B4</f>
         <v>Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="C4" s="8" t="str">
+      <c r="C4" s="12" t="str">
         <f>cross_sector_insights_tk!D4</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="13" t="str">
         <f>cross_sector_insights_tk!H4&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E4" s="9" t="str">
+      <c r="E4" s="13" t="str">
         <f>cross_sector_insights_tk!I4</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>158</v>
+      <c r="F4" s="12" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:6">
-      <c r="A5" s="8" t="str">
+      <c r="A5" s="12" t="str">
         <f>cross_sector_insights_tk!A5</f>
         <v>TK06</v>
       </c>
-      <c r="B5" s="8" t="str">
+      <c r="B5" s="12" t="str">
         <f>cross_sector_insights_tk!B5</f>
         <v>Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="12" t="str">
         <f>cross_sector_insights_tk!D5</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D5" s="9" t="str">
+      <c r="D5" s="13" t="str">
         <f>cross_sector_insights_tk!H5&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E5" s="9" t="str">
+      <c r="E5" s="13" t="str">
         <f>cross_sector_insights_tk!I5</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>159</v>
+      <c r="F5" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:6">
-      <c r="A6" s="8" t="str">
+      <c r="A6" s="12" t="str">
         <f>cross_sector_insights_tk!A6</f>
         <v>TK07</v>
       </c>
-      <c r="B6" s="8" t="str">
+      <c r="B6" s="12" t="str">
         <f>cross_sector_insights_tk!B6</f>
         <v>Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="C6" s="8" t="str">
+      <c r="C6" s="12" t="str">
         <f>cross_sector_insights_tk!D6</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="13" t="str">
         <f>cross_sector_insights_tk!H6&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E6" s="9" t="str">
+      <c r="E6" s="13" t="str">
         <f>cross_sector_insights_tk!I6</f>
         <v>Construction; Manufacturing</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>160</v>
+      <c r="F6" s="12" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" ht="51" spans="1:6">
-      <c r="A7" s="8" t="str">
+      <c r="A7" s="12" t="str">
         <f>cross_sector_insights_tk!A7</f>
         <v>TK08</v>
       </c>
-      <c r="B7" s="8" t="str">
+      <c r="B7" s="12" t="str">
         <f>cross_sector_insights_tk!B7</f>
         <v>Immediate Embodied Response to Changing Conditions</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="12" t="str">
         <f>cross_sector_insights_tk!D7</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D7" s="9" t="str">
+      <c r="D7" s="13" t="str">
         <f>cross_sector_insights_tk!H7&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E7" s="9" t="str">
+      <c r="E7" s="13" t="str">
         <f>cross_sector_insights_tk!I7</f>
         <v>Construction; Health Services</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>161</v>
+      <c r="F7" s="12" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:6">
-      <c r="A8" s="8" t="str">
+      <c r="A8" s="12" t="str">
         <f>cross_sector_insights_tk!A8</f>
         <v>TK09</v>
       </c>
-      <c r="B8" s="8" t="str">
+      <c r="B8" s="12" t="str">
         <f>cross_sector_insights_tk!B8</f>
         <v>Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="C8" s="8" t="str">
+      <c r="C8" s="12" t="str">
         <f>cross_sector_insights_tk!D8</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="13" t="str">
         <f>cross_sector_insights_tk!H8&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E8" s="9" t="str">
+      <c r="E8" s="13" t="str">
         <f>cross_sector_insights_tk!I8</f>
         <v>Manufacturing; Health Services</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>162</v>
+      <c r="F8" s="12" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="8" t="str">
+      <c r="A9" s="12" t="str">
         <f>cross_sector_insights_tk!A9</f>
         <v>TK10</v>
       </c>
-      <c r="B9" s="8" t="str">
+      <c r="B9" s="12" t="str">
         <f>cross_sector_insights_tk!B9</f>
         <v>Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" s="12" t="str">
         <f>cross_sector_insights_tk!D9</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="D9" s="13" t="str">
         <f>cross_sector_insights_tk!H9&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E9" s="9" t="str">
+      <c r="E9" s="13" t="str">
         <f>cross_sector_insights_tk!I9</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>163</v>
+      <c r="F9" s="12" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="10" ht="51" spans="1:6">
-      <c r="A10" s="8" t="str">
+      <c r="A10" s="12" t="str">
         <f>cross_sector_insights_tk!A10</f>
         <v>TK11</v>
       </c>
-      <c r="B10" s="8" t="str">
+      <c r="B10" s="12" t="str">
         <f>cross_sector_insights_tk!B10</f>
         <v>Informal Coordination, Communication, and Escalation Know-how</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" s="12" t="str">
         <f>cross_sector_insights_tk!D10</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="13" t="str">
         <f>cross_sector_insights_tk!H10&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E10" s="9" t="str">
+      <c r="E10" s="13" t="str">
         <f>cross_sector_insights_tk!I10</f>
         <v>Construction; Health Services</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>164</v>
+      <c r="F10" s="12" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="8" t="str">
+      <c r="A11" s="12" t="str">
         <f>cross_sector_insights_tk!A11</f>
         <v>TK12</v>
       </c>
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="12" t="str">
         <f>cross_sector_insights_tk!B11</f>
         <v>Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="C11" s="8" t="str">
+      <c r="C11" s="12" t="str">
         <f>cross_sector_insights_tk!D11</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D11" s="9" t="str">
+      <c r="D11" s="13" t="str">
         <f>cross_sector_insights_tk!H11&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E11" s="9" t="str">
+      <c r="E11" s="13" t="str">
         <f>cross_sector_insights_tk!I11</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>165</v>
+      <c r="F11" s="12" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4755,266 +5013,266 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="25.515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="34.765625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="23.171875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="33.8515625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="32.9375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="23.0390625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.4375" style="5"/>
+    <col min="1" max="1" width="12.109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="25.515625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="23.171875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="50.515625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="32.9375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="23.0390625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.4375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" ht="17" spans="1:8">
-      <c r="A1" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A2" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A3" s="5" t="s">
+    <row r="1" s="9" customFormat="1" ht="17" spans="1:8">
+      <c r="A1" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="D1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A4" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="G1" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="2" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A2" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A3" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="10"/>
+    </row>
+    <row r="4" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A4" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A5" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A5" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A6" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E5" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A6" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A7" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="E6" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A7" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A8" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="E7" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A8" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A9" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="E8" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A9" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" s="5" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A10" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="E9" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" s="9" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A10" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" s="5" customFormat="1" spans="1:8">
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" s="5" customFormat="1" spans="1:8">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="E10" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" s="9" customFormat="1" spans="1:8">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" s="9" customFormat="1" spans="1:8">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5028,294 +5286,294 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.0078125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24.8671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.8671875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="26.0390625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="41.1484375" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.4375" style="5"/>
+    <col min="1" max="1" width="16.6640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="19.0078125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="24.8671875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="27.8671875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="26.0390625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="41.1484375" style="9" customWidth="1"/>
+    <col min="7" max="16384" width="8.4375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:7">
-      <c r="A1" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A2" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E2" s="5" t="s">
+    <row r="1" s="9" customFormat="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A2" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A3" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A3" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="4" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A4" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A5" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="G3" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A4" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A5" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A6" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="6" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A7" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="G7" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A8" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A8" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A9" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="E9" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A10" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A11" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" s="9" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A12" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A9" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="10" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A10" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A11" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="12" s="5" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A12" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>270</v>
+      <c r="G12" s="9" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="6:6">
-      <c r="F19" s="5" t="s">
-        <v>271</v>
+      <c r="F19" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -5339,255 +5597,255 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B1" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C1" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="D1" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="F1" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="G1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:7">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="G2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:7">
       <c r="A3" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F3" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G3" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" ht="409.5" spans="1:7">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" ht="409.5" spans="1:7">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F5" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G5" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:7">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="G6" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" ht="409.5" spans="1:7">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="G7" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="409.5" spans="1:7">
       <c r="A8" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="G8" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" ht="409.5" spans="1:7">
       <c r="A9" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="F9" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="G9" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" ht="409.5" spans="1:7">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="G10" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" ht="409.5" spans="1:7">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="F11" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="G11" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -5613,97 +5871,100 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:8">
-      <c r="A1" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>320</v>
+      <c r="A1" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="D1" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:8">
-      <c r="A2" s="3" t="s">
-        <v>322</v>
+      <c r="A2" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:8">
-      <c r="A3" s="3" t="s">
-        <v>330</v>
+      <c r="A3" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="4" ht="409.5" spans="1:8">
-      <c r="A4" s="3" t="s">
-        <v>335</v>
+      <c r="A4" s="7" t="s">
+        <v>350</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" ht="409.5" spans="1:8">
       <c r="A5" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:8">
       <c r="A6" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>343</v>
+        <v>357</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -5715,155 +5976,210 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="17.578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="55.3359375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.9453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:2">
+    <row r="1" ht="17" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" ht="17" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" ht="17" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" ht="17" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" ht="17" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" ht="17" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" ht="17" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4" ht="17" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" ht="17" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" ht="17" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="7" ht="17" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="8" ht="17" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="9" ht="17" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" ht="17" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="11" ht="17" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" ht="17" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="13" ht="17" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="14" ht="17" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="15" ht="17" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="16" ht="17" spans="1:2">
-      <c r="A16" s="1" t="s">
+    </row>
+    <row r="8" ht="17" spans="1:3">
+      <c r="A8" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="17" ht="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+      <c r="C8" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:3">
+      <c r="A9" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="18" ht="17" spans="1:2">
-      <c r="A18" s="1" t="s">
+      <c r="C9" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:3">
+      <c r="A10" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>379</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" ht="17" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" ht="17" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="16" ht="17" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="17" ht="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/src/conf/cross_sector_insight/cross_sector_insights.xlsx
+++ b/src/conf/cross_sector_insight/cross_sector_insights.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11240" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="11120" firstSheet="4" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="cross_sector_insights_tp" sheetId="4" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="s003_insights" sheetId="1" r:id="rId7"/>
     <sheet name="pattern type" sheetId="8" r:id="rId8"/>
     <sheet name="potenial patterns" sheetId="10" r:id="rId9"/>
+    <sheet name="TP07–TK10" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cross_sector_insights_tp!$A$1:$H$16</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="497">
   <si>
     <t>ID</t>
   </si>
@@ -359,6 +360,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>cross-industry</t>
     </r>
     <r>
@@ -386,6 +393,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>cross-industry</t>
     </r>
     <r>
@@ -1592,43 +1605,67 @@
     <t>&lt;TP03,TK06&gt;</t>
   </si>
   <si>
-    <t>MATCH (tp:TechnologyenablePractice)-[r]-(tk:TacitKnowledge) 
-WHERE tp.node_id = 'h001M01TP03' AND tk.node_id = 'h001M01TK06'
-WITH tp, COLLECT({src_node:tp, rel: r, dst_node: tk}) AS tp_tk_By,
-COLLECT(DISTINCT tk) AS tp_tk_list
-OPTIONAL MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
-WHERE (a = tp OR a in tp_tk_list) AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH tp, tp_tk_By, tp_tk_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_By,
-COLLECT(DISTINCT b) AS tp_r_list
-OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
-WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH tp, tp_tk_By, tp_tk_list, tp_r_By,tp_r_list,
-COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
-COLLECT(DISTINCT b) AS tp_child_list
+    <t xml:space="preserve">MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE (a.node_id = 'h001M01TP03' OR a.node_id = 'h001M01TK06') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' AND NOT (b.node_id CONTAINS 'LI13' OR b.node_id CONTAINS 'LI14')
+WITH COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_dep,
+COLLECT(DISTINCT b) AS c_r_list
 OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
-WHERE a in tp_tk_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_child_by,
-COLLECT(DISTINCT b) AS tk_child_list
+WHERE (a.node_id = 'h001M01TP03' OR a.node_id = 'h001M01TK06') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_child,
+COLLECT(DISTINCT b) AS c_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a IN c_child_list AND b IN c_child_list
+WITH c_r_dep, c_r_child,c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_c_child,
+COLLECT(DISTINCT b) AS c_child_list
 OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
-WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
-COLLECT(DISTINCT b) AS tp_r_child_list
+WHERE a in c_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list, c_r_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_r_child,
+COLLECT(DISTINCT b) AS r_child_list
 OPTIONAL MATCH (a)-[r]-(b)
-WHERE a in tp_child_list AND b in tp_r_child_list
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_childBy
+WHERE a in c_child_list AND b in r_child_list
+WITH c_r_dep, c_r_child,dep_r_child, c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_dep_child
 OPTIONAL MATCH (a)-[r]-(b)
-WHERE a in tk_child_list AND b in tp_r_child_list
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,tp_r_childBy,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_r_childBy
-OPTIONAL MATCH (a)-[r]-(b)
-WHERE a in tp_child_list AND b in tk_child_list
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, tk_r_childBy,tp_r_childBy,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_tk_childBy
-RETURN tp, tp_tk_By,tp_child_By,tk_child_by,tp_r_child_by,tk_r_childBy,tp_r_childBy</t>
+WHERE a.node_id = 'h001M01TP07' AND b.node_id = 'h001M01TK10'
+WITH c_r_dep, c_r_child,dep_r_child, c_child_r_dep_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_c
+// ========== 1. 清洗：去掉 rel 为 null 的占位 ==========
+WITH [x IN c_r_dep     WHERE x.rel IS NOT NULL] AS c_r_dep,
+     [x IN c_r_child WHERE x.rel IS NOT NULL] AS c_r_child,
+     [x IN dep_r_child WHERE x.rel IS NOT NULL] AS dep_r_child,
+     [x IN c_child_r_dep_child  WHERE x.rel IS NOT NULL] AS c_child_r_dep_child,
+     [x IN c_r_c       WHERE x.rel IS NOT NULL] AS c_r_c,
+     [x IN c_child_r_c_child       WHERE x.rel IS NOT NULL] AS c_child_r_c_child
+// ========== 2. 合并所有输出边 = 输出子图 ==========
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     c_r_dep + c_r_child + dep_r_child + c_child_r_dep_child + c_r_c + c_child_r_c_child AS all_edges
+// ========== 3. 在子图内统计每个节点的度数（出入度之和）==========
+UNWIND all_edges AS e
+UNWIND [e.src_node, e.dst_node] AS n
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c, c_child_r_c_child,
+     elementId(n) AS nid, count(*) AS sub_deg
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     collect([nid, sub_deg]) AS pairs
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     apoc.map.fromPairs(pairs) AS deg_map
+// ========== 4. 用子图度数过滤（≠ 1）==========
+RETURN
+  [x IN c_r_c       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_c,
+  [x IN c_r_dep     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_dep,
+  [x IN c_r_child     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_child,
+  [x IN dep_r_child WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS dep_r_child,
+  [x IN c_child_r_c_child       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_c_child,
+  [x IN c_child_r_dep_child  WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_dep_child;
+</t>
   </si>
   <si>
     <t xml:space="preserve">You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
@@ -1638,51 +1675,78 @@
 - Definition:  A comparable TP is associated with comparable TK forms across all three sectors. 
 - Purpose: Identifies the strongest evidence of a cross-sector common retention configuration and helps reveal what may transcend sector boundaries at both the practice and knowledge-target levels.
 ***Input data***
-Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
-MATCH (tp:TechnologyenablePractice)-[r]-(tk:TacitKnowledge) 
-WHERE tp.node_id = 'h001M01TP03' AND tk.node_id = 'h001M01TK06'
-WITH tp, COLLECT({src_node:tp, rel: r, dst_node: tk}) AS tp_tk_By,
-COLLECT(DISTINCT tk) AS tp_tk_list
-OPTIONAL MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
-WHERE (a = tp OR a in tp_tk_list) AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH tp, tp_tk_By, tp_tk_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_By,
-COLLECT(DISTINCT b) AS tp_r_list
-OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b)
-WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH tp, tp_tk_By, tp_tk_list, tp_r_By,tp_r_list,
-COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By,
-COLLECT(DISTINCT b) AS tp_child_list
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:
+MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE (a.node_id = 'h001M01TP03' OR a.node_id = 'h001M01TK06') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' AND NOT (b.node_id CONTAINS 'LI13' OR b.node_id CONTAINS 'LI14')
+WITH COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_dep,
+COLLECT(DISTINCT b) AS c_r_list
 OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
-WHERE a in tp_tk_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_child_by,
-COLLECT(DISTINCT b) AS tk_child_list
+WHERE (a.node_id = 'h001M01TP03' OR a.node_id = 'h001M01TK06') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_child,
+COLLECT(DISTINCT b) AS c_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a IN c_child_list AND b IN c_child_list
+WITH c_r_dep, c_r_child,c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_c_child,
+COLLECT(DISTINCT b) AS c_child_list
 OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
-WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by,
-COLLECT(DISTINCT b) AS tp_r_child_list
+WHERE a in c_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list, c_r_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_r_child,
+COLLECT(DISTINCT b) AS r_child_list
 OPTIONAL MATCH (a)-[r]-(b)
-WHERE a in tp_child_list AND b in tp_r_child_list
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_childBy
+WHERE a in c_child_list AND b in r_child_list
+WITH c_r_dep, c_r_child,dep_r_child, c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_dep_child
 OPTIONAL MATCH (a)-[r]-(b)
-WHERE a in tk_child_list AND b in tp_r_child_list
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,tp_r_childBy,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_r_childBy
-OPTIONAL MATCH (a)-[r]-(b)
-WHERE a in tp_child_list AND b in tk_child_list
-WITH  tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, tk_r_childBy,tp_r_childBy,
-COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_tk_childBy
-RETURN tp, tp_tk_By,tp_child_By,tk_child_by,tp_r_child_by,tk_r_childBy,tp_r_childBy
+WHERE a.node_id = 'h001M01TP07' AND b.node_id = 'h001M01TK10'
+WITH c_r_dep, c_r_child,dep_r_child, c_child_r_dep_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_c
+// ========== 1. 清洗：去掉 rel 为 null 的占位 ==========
+WITH [x IN c_r_dep     WHERE x.rel IS NOT NULL] AS c_r_dep,
+     [x IN c_r_child WHERE x.rel IS NOT NULL] AS c_r_child,
+     [x IN dep_r_child WHERE x.rel IS NOT NULL] AS dep_r_child,
+     [x IN c_child_r_dep_child  WHERE x.rel IS NOT NULL] AS c_child_r_dep_child,
+     [x IN c_r_c       WHERE x.rel IS NOT NULL] AS c_r_c,
+     [x IN c_child_r_c_child       WHERE x.rel IS NOT NULL] AS c_child_r_c_child
+// ========== 2. 合并所有输出边 = 输出子图 ==========
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     c_r_dep + c_r_child + dep_r_child + c_child_r_dep_child + c_r_c + c_child_r_c_child AS all_edges
+// ========== 3. 在子图内统计每个节点的度数（出入度之和）==========
+UNWIND all_edges AS e
+UNWIND [e.src_node, e.dst_node] AS n
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c, c_child_r_c_child,
+     elementId(n) AS nid, count(*) AS sub_deg
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     collect([nid, sub_deg]) AS pairs
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     apoc.map.fromPairs(pairs) AS deg_map
+// ========== 4. 用子图度数过滤（≠ 1）==========
+RETURN
+  [x IN c_r_c       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_c,
+  [x IN c_r_dep     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_dep,
+  [x IN c_r_child     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_child,
+  [x IN dep_r_child WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS dep_r_child,
+  [x IN c_child_r_c_child       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_c_child,
+  [x IN c_child_r_dep_child  WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_dep_child;
+Mandatory analytical procedure
+1. The subgraph structure consists of layer 0 (node ID prefix h001) and layer 1 (node ID prefix s00), with the relationship is_an_instance_of connecting nodes between layer 0 and layer 1.
+2. Examine the environmental dependencies, organizational dependencies, and limitation of each node in layer 0, treating them as candidate insights, and identify the corresponding child nodes’ `evidence_statement` attributes as supporting evidence for further analysis.
+3. Summarize external resource dependencies from environmental dependencies; identify internal resource and capability dependencies, as well as organizational cultural dependencies, from organizational dependencies. 
+4. Supplement and consolidate the above dependencies based on the constraints.
 ***Output Structure***
 Pattern Name: &lt;TP03, TK06&gt;  &lt;please name it&gt;
 Pattern Type: Cross-sector TP–TK convergence
 Technology-enable Practice Definition: Uses technologies like VR, AR, MR, CAVE, or hybrid XR environments to support embodied rehearsal, contextual guidance, historical interpretation, hazard recognition, and situated knowledge transfer.
 Quality Assessment: &lt;please assess the pattern in 100 word&gt;
-Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP03 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node&gt;  
-Mechanism-based transfer considerations: &lt;Please analyze this pattern from aspects such as the basic mechanism, potential transfer scenarios, resource and environmental dependencies, organizational culture dependencies, and other limitations, and provide a 200-word explanation.&gt;
+Mechanism-based transfer considerations: &lt;Please analyze this pattern from aspects such as the basic mechanism, potential transfer scenarios, resource and environmental dependencies, organizational culture dependencies, and other limitations, and provide a 500-word explanation.&gt;
 </t>
   </si>
   <si>
@@ -1753,7 +1817,7 @@
 - Definition:  A comparable TP is associated with comparable TK forms within a sector pair or a particular sector configuration, but this convergence is not observed across all three sectors.
 - Purpose: Identifies bounded commonality, showing that some retention configurations may be shared between particular contexts rather than being broadly cross-sector. This helps establish the boundary conditions of apparent generality.
 ***Input data***
-Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation) 
+Use [$analyze-neo4j-knowledge-graph] to execute the following Cypher query:
 MATCH (tp:TechnologyenablePractice)-[r]-(b:TacitKnowledge|EnvironmentalDependency|OrganizationalDependency|Limitation)
 WHERE tp.node_id = 'h001M01TP15' AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
 WITH tp, COLLECT({src_node:tp, rel: r, dst_node: b}) AS tpBy,
@@ -1782,6 +1846,68 @@
 </t>
   </si>
   <si>
+    <t>MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE (a.node_id = 'h001M01TP07' OR a.node_id = 'h001M01TK10') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' AND NOT (b.node_id CONTAINS 'LI13' OR b.node_id CONTAINS 'LI14')
+WITH COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_dep,
+COLLECT(DISTINCT b) AS c_r_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE (a.node_id = 'h001M01TP07' OR a.node_id = 'h001M01TK10') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_child,
+COLLECT(DISTINCT b) AS c_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a IN c_child_list AND b IN c_child_list
+WITH c_r_dep, c_r_child,c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_c_child,
+COLLECT(DISTINCT b) AS c_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in c_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list, c_r_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_r_child,
+COLLECT(DISTINCT b) AS r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in c_child_list AND b in r_child_list
+WITH c_r_dep, c_r_child,dep_r_child, c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_dep_child
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a.node_id = 'h001M01TP07' AND b.node_id = 'h001M01TK10'
+WITH c_r_dep, c_r_child,dep_r_child, c_child_r_dep_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_c
+// ========== 1. 清洗：去掉 rel 为 null 的占位 ==========
+WITH [x IN c_r_dep     WHERE x.rel IS NOT NULL] AS c_r_dep,
+     [x IN c_r_child WHERE x.rel IS NOT NULL] AS c_r_child,
+     [x IN dep_r_child WHERE x.rel IS NOT NULL] AS dep_r_child,
+     [x IN c_child_r_dep_child  WHERE x.rel IS NOT NULL] AS c_child_r_dep_child,
+     [x IN c_r_c       WHERE x.rel IS NOT NULL] AS c_r_c,
+     [x IN c_child_r_c_child       WHERE x.rel IS NOT NULL] AS c_child_r_c_child
+// ========== 2. 合并所有输出边 = 输出子图 ==========
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     c_r_dep + c_r_child + dep_r_child + c_child_r_dep_child + c_r_c + c_child_r_c_child AS all_edges
+// ========== 3. 在子图内统计每个节点的度数（出入度之和）==========
+UNWIND all_edges AS e
+UNWIND [e.src_node, e.dst_node] AS n
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c, c_child_r_c_child,
+     elementId(n) AS nid, count(*) AS sub_deg
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     collect([nid, sub_deg]) AS pairs
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     apoc.map.fromPairs(pairs) AS deg_map
+// ========== 4. 用子图度数过滤（≠ 1）==========
+RETURN
+  [x IN c_r_c       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_c,
+  [x IN c_r_dep     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_dep,
+  [x IN c_r_child     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_child,
+  [x IN dep_r_child WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS dep_r_child,
+  [x IN c_child_r_c_child       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_c_child,
+  [x IN c_child_r_dep_child  WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_dep_child;</t>
+  </si>
+  <si>
     <t>You are an expert academic scholar with interdisciplinary expertise in knowledge management, emerging technologies, organizational capabilities, and innovation.
 ***Task***  Analyze the knowledge graphs extracted from multiple cases and conduct a qualitative analysis to assess whether this sub-group can validate that &lt;TP07, TK10&gt; belongs to this pattern type. During the analytical process, all claims you generate should be supported by the evidence in the knowledge graphs. @@ -1789,51 +1915,78 @@
 - Definition: A comparable TP is associated with comparable TK forms within a sector pair or a particular sector configuration, but this convergence is not observed across all three sectors.  - Purpose: Identifies bounded commonality, showing that some retention configurations may be shared between particular contexts rather than being broadly cross-sector. This helps establish the boundary conditions of apparent generality.
 ***Input data*** -Use [[$analyze-neo4j-knowledge-graph](/Users/meimei/.codex/skills/analyze-neo4j-knowledge-graph/SKILL.md)] to execute the following Cypher query:MATCH (tk:TacitKnowledge)-[r]-(b:TechnologyenablePractice|Limitation)  -MATCH (tp:TechnologyenablePractice)-[r]-(tk:TacitKnowledge)  -WHERE tp.node_id = 'h001M01TP07’ AND tk.node_id = 'h001M01TK10’ -WITH tp, COLLECT({src_node:tp, rel: r, dst_node: tk}) AS tp_tk_By, -COLLECT(DISTINCT tk) AS tp_tk_list
-OPTIONAL MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation) -WHERE (a = tp OR a in tp_tk_list) AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' -WITH tp, tp_tk_By, tp_tk_list, -COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_By, -COLLECT(DISTINCT b) AS tp_r_list
-OPTIONAL MATCH (tp)-[r:is_an_instance_of]-(b) -WHERE NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' -WITH tp, tp_tk_By, tp_tk_list, tp_r_By,tp_r_list, -COLLECT({src_node:tp, rel: r, dst_node: b}) AS tp_child_By, -COLLECT(DISTINCT b) AS tp_child_list
-OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b) -WHERE a in tp_tk_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' -WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list, -COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_child_by, -COLLECT(DISTINCT b) AS tk_child_list
-OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b) -WHERE a in tp_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' -WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list, -COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_child_by, -COLLECT(DISTINCT b) AS tp_r_child_list
-OPTIONAL MATCH (a)-[r]-(b) -WHERE a in tp_child_list AND b in tp_r_child_list -WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, -COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_r_childBy
-OPTIONAL MATCH (a)-[r]-(b) -WHERE a in tk_child_list AND b in tp_r_child_list -WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list,tp_r_childBy, -COLLECT({src_node:a, rel: r, dst_node: b}) AS tk_r_childBy
-OPTIONAL MATCH (a)-[r]-(b) -WHERE a in tp_child_list AND b in tk_child_list -WITH tp, tp_tk_By,tp_r_list,tp_child_By,tp_child_list,tk_child_by, tk_child_list,tp_r_child_by,tp_r_child_list, tk_r_childBy,tp_r_childBy, -COLLECT({src_node:a, rel: r, dst_node: b}) AS tp_tk_childBy
-RETURN tp, tp_tk_By,tp_child_By,tk_child_by,tp_r_child_by,tk_r_childBy,tp_r_childBy
+Use [[$analyze-neo4j-knowledge-graph](/Users/meimei/.codex/skills/analyze-neo4j-knowledge-graph/SKILL.md)] to execute the following Cypher query: +MATCH (a)-[r]-(b:EnvironmentalDependency|OrganizationalDependency|Limitation)
+WHERE (a.node_id = 'h001M01TP07' OR a.node_id = 'h001M01TK10') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous' AND NOT (b.node_id CONTAINS 'LI13' OR b.node_id CONTAINS 'LI14')
+WITH COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_dep,
+COLLECT(DISTINCT b) AS c_r_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE (a.node_id = 'h001M01TP07' OR a.node_id = 'h001M01TK10') AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_child,
+COLLECT(DISTINCT b) AS c_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a IN c_child_list AND b IN c_child_list
+WITH c_r_dep, c_r_child,c_r_list,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_c_child,
+COLLECT(DISTINCT b) AS c_child_list
+OPTIONAL MATCH (a)-[r:is_an_instance_of]-(b)
+WHERE a in c_r_list AND NOT coalesce(b.node_name, '') STARTS WITH 'Ambiguous'
+WITH c_r_dep, c_r_list, c_r_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS dep_r_child,
+COLLECT(DISTINCT b) AS r_child_list
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a in c_child_list AND b in r_child_list
+WITH c_r_dep, c_r_child,dep_r_child, c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_child_r_dep_child
+OPTIONAL MATCH (a)-[r]-(b)
+WHERE a.node_id = 'h001M01TP07' AND b.node_id = 'h001M01TK10'
+WITH c_r_dep, c_r_child,dep_r_child, c_child_r_dep_child,c_child_list,c_child_r_c_child,
+COLLECT({src_node:a, rel: r, dst_node: b}) AS c_r_c
+// ========== 1. 清洗：去掉 rel 为 null 的占位 ==========
+WITH [x IN c_r_dep     WHERE x.rel IS NOT NULL] AS c_r_dep,
+     [x IN c_r_child WHERE x.rel IS NOT NULL] AS c_r_child,
+     [x IN dep_r_child WHERE x.rel IS NOT NULL] AS dep_r_child,
+     [x IN c_child_r_dep_child  WHERE x.rel IS NOT NULL] AS c_child_r_dep_child,
+     [x IN c_r_c       WHERE x.rel IS NOT NULL] AS c_r_c,
+     [x IN c_child_r_c_child       WHERE x.rel IS NOT NULL] AS c_child_r_c_child
+// ========== 2. 合并所有输出边 = 输出子图 ==========
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     c_r_dep + c_r_child + dep_r_child + c_child_r_dep_child + c_r_c + c_child_r_c_child AS all_edges
+// ========== 3. 在子图内统计每个节点的度数（出入度之和）==========
+UNWIND all_edges AS e
+UNWIND [e.src_node, e.dst_node] AS n
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c, c_child_r_c_child,
+     elementId(n) AS nid, count(*) AS sub_deg
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     collect([nid, sub_deg]) AS pairs
+WITH c_r_dep, c_r_child, dep_r_child, c_child_r_dep_child, c_r_c,c_child_r_c_child,
+     apoc.map.fromPairs(pairs) AS deg_map
+// ========== 4. 用子图度数过滤（≠ 1）==========
+RETURN
+  [x IN c_r_c       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_c,
+  [x IN c_r_dep     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_dep,
+  [x IN c_r_child     WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_r_child,
+  [x IN dep_r_child WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS dep_r_child,
+  [x IN c_child_r_c_child       WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_c_child,
+  [x IN c_child_r_dep_child  WHERE deg_map[elementId(x.src_node)] &lt;&gt; 1
+                   AND   deg_map[elementId(x.dst_node)] &lt;&gt; 1] AS c_child_r_dep_child;
+***Mandatory analytical procedure***
+1. The subgraph structure consists of layer 0 (node ID prefix h001) and layer 1 (node ID prefix s00), with the relationship is_an_instance_of connecting nodes between layer 0 and layer 1.
+2. Examine the environmental dependencies, organizational dependencies, and limitation of each node in layer 0, treating them as candidate insights, and identify the corresponding child nodes’ `evidence_statement` attributes as supporting evidence for further analysis.
+3. Summarize external resource dependencies from environmental dependencies; identify internal resource and capability dependencies, as well as organizational cultural dependencies, from organizational dependencies. 
+4. Supplement and consolidate the above dependencies based on the constraints.
 ***Output Structure***  Pattern Name: &lt;TP07, TK10&gt; &lt;please name it&gt;  Pattern Type: Context-bounded TP–TK convergence  Technology-enable Practice Definition: Uses AI, machine learning, NLP, statistical learning, or rule-based algorithms to derive classifications, forecasts, detected patterns, and predicted conditions from data.
 Quality Assessment: &lt;please assess the pattern in 100 word&gt;
-Evidence Chain:&lt;draw a svg figure to exhibit the evidence from the center TP07 to industry-level to case-levle, mark the tacit knowledge and technology-enable practice in each node, you just need keep sectors which keep relevant evidences&gt;  
-Mechanism-based transfer considerations: &lt;Please analyze this pattern from aspects such as the basic mechanism, potential transfer scenarios, resource and environmental dependencies, organizational culture dependencies, and other limitations, and provide a 200-word explanation.&gt;</t>
+Mechanism-based transfer considerations: &lt;Please analyze this pattern from aspects such as the basic mechanism, potential transfer scenarios, resource and environmental dependencies, organizational culture dependencies, and other limitations, and provide a 500-word explanation.&gt;</t>
   </si>
   <si>
     <t>TK variation across TPs</t>
@@ -2145,6 +2298,594 @@
   </si>
   <si>
     <t>Criteria-Based Evaluation of Professional Judgment</t>
+  </si>
+  <si>
+    <t>node_name</t>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>evidence</t>
+  </si>
+  <si>
+    <t>h001M01ED01</t>
+  </si>
+  <si>
+    <t>Political, Regulatory &amp; Jurisdictional Environment Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Environmental dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Algorithms must align with construction-safety legislation, reporting rules, privacy requirements and jurisdiction-specific risk standards.</t>
+    </r>
+  </si>
+  <si>
+    <t>Accident data came from government safety sources; safety decisions followed Australian, Chinese and Peruvian regulations (c002;c008;c011;c016).</t>
+  </si>
+  <si>
+    <t>政治法规约束下的安全治理，自然环境对建筑灾害，和外部技术基础设施决定的技术生态的准备程度；同时，组织内部AI adoption required management-backed resource allocation，包括资金，专家团队重建，技术与管理流水线的配合，以及</t>
+  </si>
+  <si>
+    <t>h001M01ED04</t>
+  </si>
+  <si>
+    <t>Natural &amp; Climatic Environment Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Environmental dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Models require current weather and seasonal data because climatic conditions alter hazards, heating demand and operational baselines.</t>
+    </r>
+  </si>
+  <si>
+    <t>Wind and sandstorms shaped bridge hazards, while weather and autumn–winter conditions affected building-temperature prediction (c005;c017).</t>
+  </si>
+  <si>
+    <t>h001M01ED05</t>
+  </si>
+  <si>
+    <t>External Technological &amp; Infrastructure Environment Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Environmental dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Reliable connectivity, transmission capacity, cloud services and external databases condition data-intensive deployment.</t>
+    </r>
+  </si>
+  <si>
+    <t>Rural point-cloud transmission had a substantially higher failure rate than urban transmission; bid automation also required integrated digital information infrastructure (c001;c009).</t>
+  </si>
+  <si>
+    <t>h001M01ED06</t>
+  </si>
+  <si>
+    <t>Client, Procurement &amp; Institutional Environment Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Environmental dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Predictions and extracted knowledge must reflect changing client requirements, submission rules, deadlines and procurement criteria.</t>
+    </r>
+  </si>
+  <si>
+    <t>Construction bids required project-specific tailoring and compliance with document, deadline and quality–cost evaluation requirements (c007;c009).</t>
+  </si>
+  <si>
+    <t>h001M01ED07</t>
+  </si>
+  <si>
+    <t>Supply-Chain &amp; Logistical Environment Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Environmental dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Continuous access to documents, data sources, sensors and technical inputs is vulnerable to logistical and geopolitical disruption.</t>
+    </r>
+  </si>
+  <si>
+    <t>Megaproject operation was conditioned by logistical complexity and geopolitical instability (c014).</t>
+  </si>
+  <si>
+    <t>h001M01ED08</t>
+  </si>
+  <si>
+    <t>Geographic &amp; Physical Site Context Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Environmental dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Models require access to observable, site-specific conditions rather than relying solely on generalized datasets.</t>
+    </r>
+  </si>
+  <si>
+    <t>Evidence covers remote mountainous locations, congested bridge sites, over-water work, confined spaces and worker-specific job sites (c001;c005;c006;c011).</t>
+  </si>
+  <si>
+    <t>h001M01LI01</t>
+  </si>
+  <si>
+    <t>Individual Knowledge and Memory Decay Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Retention limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Algorithmically presented professional standards still require reinforcement because exposure does not ensure durable retention.</t>
+    </r>
+  </si>
+  <si>
+    <t>Safety knowledge declined after four to five weeks, and some learners reportedly forgot most content within a week (c002;c004;c011).</t>
+  </si>
+  <si>
+    <t>h001M01LI03</t>
+  </si>
+  <si>
+    <t>Human Physiological, Cognitive-Capacity and Demographic Constraints Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>User-capability limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Interfaces and explanations must accommodate age, working-memory limits, prior expertise and mixed learning preferences.</t>
+    </r>
+  </si>
+  <si>
+    <t>Older trainees experienced controller difficulty; multimedia effectiveness varied by expertise, and learners displayed non-fixed preferences (c005;c010;c011).</t>
+  </si>
+  <si>
+    <t>h001M01LI04</t>
+  </si>
+  <si>
+    <t>Instructional Design, Delivery, Assessment and Transfer Shortcomings Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Transfer limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Predictions must be embedded in active, contextual instruction and workplace feedback rather than delivered as decontextualized information.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cases found passive learning, cognitive overload, incomplete hazard recognition and gaps between acquired knowledge and site behaviour (c002;c004;c005;c010).</t>
+  </si>
+  <si>
+    <t>h001M01LI05</t>
+  </si>
+  <si>
+    <t>Software, Algorithmic, Data Quality and Interoperability Barriers Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Technical capability limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Deployment requires data cleaning, standardized formats, domain dictionaries, OCR, interoperability and uncertainty management.</t>
+    </r>
+  </si>
+  <si>
+    <t>Accident reports were unstructured, language-specific and prone to vocabulary-based misclassification; bid extraction supported only PDFs and lacked OCR (c008;c009).</t>
+  </si>
+  <si>
+    <t>h001M01LI06</t>
+  </si>
+  <si>
+    <t>Hardware, Sensor and Technical Infrastructure Constraints Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Internal resource limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Adequate computing, sensing, connectivity and controllable physical infrastructure are prerequisites for real-time prediction.</t>
+    </r>
+  </si>
+  <si>
+    <t>Insufficient infrastructure restricted AI monitoring, while incomplete building sectorization limited the precision of heating decisions (c014;c017).</t>
+  </si>
+  <si>
+    <t>h001M01LI08</t>
+  </si>
+  <si>
+    <t>Time, Staffing, Expertise, Scheduling and Workload Constraints Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Resource and capability limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Automation requires protected implementation time, sufficient personnel and continuing expert involvement.</t>
+    </r>
+  </si>
+  <si>
+    <t>Text classification and bid preparation were labour-intensive, but nuanced project risks still made complete automation impractical (c008;c009;c012).</t>
+  </si>
+  <si>
+    <t>h001M01LI09</t>
+  </si>
+  <si>
+    <t>Organizational Culture, Leadership and Adoption Barriers Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Cultural limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Technical availability is insufficient without trust, incentives, management attention and willingness to use and share knowledge.</t>
+    </r>
+  </si>
+  <si>
+    <t>Knowledge hoarding and job-security fears obstructed capture; authoritarian leadership produced underuse or negligible adoption of AI tools (c007;c012;c014).</t>
+  </si>
+  <si>
+    <t>h001M01LI10</t>
+  </si>
+  <si>
+    <t>Organizational Governance Constraints Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Governance limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Organizations need stewardship, privacy controls and continuity arrangements to retain knowledge across temporary teams and staff turnover.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bid documents created third-party API confidentiality risks, while retirements, temporary teams and staff changes caused contextual knowledge loss (c007;c009;c012;c016).</t>
+  </si>
+  <si>
+    <t>h001M01LI11</t>
+  </si>
+  <si>
+    <t>Physical-Environmental and Operational Variability Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Context limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Unscheduled human activity and changing physical conditions can invalidate stable algorithmic assumptions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Building temperatures diverged from predicted thresholds because of variable occupancy, open windows, weather and inflexible heating schedules (c017).</t>
+  </si>
+  <si>
+    <t>h001M01LI13</t>
+  </si>
+  <si>
+    <t>Research Design, Measurement and Validation Flaws Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Validation-capability limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Deployment decisions require behavioural and longitudinal validation, not only model accuracy or short-term test scores.</t>
+    </r>
+  </si>
+  <si>
+    <t>Studies omitted long-term practical performance, used limited features and relied on contested learning-style constructs (c004;c010).</t>
+  </si>
+  <si>
+    <t>h001M01LI14</t>
+  </si>
+  <si>
+    <t>Empirical Sample and Generalizability Limitations Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Data-resource limitation:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Training data must cover rare events, mixed users, document formats and different project contexts.</t>
+    </r>
+  </si>
+  <si>
+    <t>Accident-class samples were small and imbalanced; bid evidence came from two firms, and mixed learner profiles were underrepresented (c008;c009;c010).</t>
+  </si>
+  <si>
+    <t>h001M01OD01</t>
+  </si>
+  <si>
+    <t>Governance, Standards &amp; Formal Control Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational capability dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Formal standards must govern data quality, privacy, access, review and acceptable algorithmic performance.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cases applied safety standards, ethics approval, mandatory inductions, consent procedures and restricted access to sensitive knowledge (c004;c009;c012).</t>
+  </si>
+  <si>
+    <t>h001M01OD02</t>
+  </si>
+  <si>
+    <t>Strategic Leadership &amp; Sponsorship Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational capability dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Senior and participative leadership must provide direction, authorize intervention and allocate implementation resources.</t>
+    </r>
+  </si>
+  <si>
+    <t>Management support strengthened safety application, while participative leadership enabled AI use, knowledge sharing and proactive action (c008;c014).</t>
+  </si>
+  <si>
+    <t>h001M01OD03</t>
+  </si>
+  <si>
+    <t>Financial, Technical &amp; Information Resources Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational resource dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Firms need funding, representative corpora, centralized information systems and implementation and training resources.</t>
+    </r>
+  </si>
+  <si>
+    <t>Deep-learning performance depended on a large accident corpus; bid automation required centralized data, and AI adoption required management-backed resource allocation (c008;c009;c014).</t>
+  </si>
+  <si>
+    <t>h001M01OD04</t>
+  </si>
+  <si>
+    <t>Time, Workload &amp; Operational Scheduling Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational resource dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Deployment requires protected time for adaptation, training, model maintenance and knowledge curation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cases allocated time for technology familiarization and training, while narrative elicitation and digital integration required dedicated organizational time (c003;c011;c012).</t>
+  </si>
+  <si>
+    <t>h001M01OD05</t>
+  </si>
+  <si>
+    <t>Human Capacity, Roles &amp; Participation Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational capability dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Domain experts, trained facilitators, digitally literate staff and participating stakeholders must interpret and validate outputs.</t>
+    </r>
+  </si>
+  <si>
+    <t>Evidence identifies workforce KM training, trained narrative facilitators, stakeholder participation and expert annotation or review as necessary roles (c007;c012;c014).</t>
+  </si>
+  <si>
+    <t>h001M01OD06</t>
+  </si>
+  <si>
+    <t>Culture, Trust &amp; Relational Climate Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational culture dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Deployment requires psychological safety, interorganizational trust, openness to digital transformation and a knowledge-sharing safety culture.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cases associate adoption with trust, openness and continuous-improvement norms and identify their absence as a barrier to sharing (c007;c009;c012;c014;c016).</t>
+  </si>
+  <si>
+    <t>h001M01OD08</t>
+  </si>
+  <si>
+    <t>Organizational Structure &amp; Process Design Collection</t>
+  </si>
+  <si>
+    <r>
+      <t>Organizational capability dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Algorithms must be integrated into dedicated functions, standardized workflows and processes responsive to project and worker differences.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dedicated bid departments, organizational maturity, information-system readiness and task-specific training design supported implementation (c002;c007;c009).</t>
   </si>
 </sst>
 </file>
@@ -2829,13 +3570,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2862,15 +3615,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -3446,9 +4190,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="26.953125" customWidth="1"/>
-    <col min="3" max="3" width="45.046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="31.546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="45.046875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="31.546875" style="5" customWidth="1"/>
     <col min="6" max="6" width="26.6484375" customWidth="1"/>
     <col min="7" max="7" width="44.65625" customWidth="1"/>
     <col min="9" max="9" width="14.703125" customWidth="1"/>
@@ -3456,114 +4200,114 @@
     <col min="11" max="11" width="22.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="26" customFormat="1" spans="1:11">
-      <c r="A1" s="27" t="s">
+    <row r="1" s="27" customFormat="1" spans="1:11">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="29" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="84" spans="1:11">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="12" t="str" cm="1">
+      <c r="E2" s="7" t="str" cm="1">
         <f t="array" ref="E2">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A2,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="F2" s="12" t="str" cm="1">
+      <c r="F2" s="7" t="str" cm="1">
         <f t="array" ref="F2">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A2,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G2" s="12" t="str" cm="1">
+      <c r="G2" s="7" t="str" cm="1">
         <f t="array" ref="G2">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A2,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="20">
         <f>3-COUNTIF(E2:G2,"")</f>
         <v>2</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:11">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="12" t="str" cm="1">
+      <c r="E3" s="7" t="str" cm="1">
         <f t="array" ref="E3">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A3,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F3" s="12" t="str" cm="1">
+      <c r="F3" s="7" t="str" cm="1">
         <f t="array" ref="F3">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A3,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G3" s="12" t="str" cm="1">
+      <c r="G3" s="7" t="str" cm="1">
         <f t="array" ref="G3">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A3,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="20">
         <f t="shared" ref="H3:H16" si="0">3-COUNTIF(E3:G3,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="168" spans="1:11">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="12" t="str" cm="1">
+      <c r="E4" s="7" t="str" cm="1">
         <f t="array" ref="E4">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A4,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
@@ -3571,14 +4315,14 @@
 TK08 Immediate Embodied Response to Changing Conditions
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F4" s="12" t="str" cm="1">
+      <c r="F4" s="7" t="str" cm="1">
         <f t="array" ref="F4">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A4,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="G4" s="12" t="str" cm="1">
+      <c r="G4" s="7" t="str" cm="1">
         <f t="array" ref="G4">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A4,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
@@ -3586,152 +4330,152 @@
 TK11 Informal Coordination, Communication, and Escalation Know-how
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" ht="68" spans="1:11">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="12" t="str" cm="1">
+      <c r="E5" s="7" t="str" cm="1">
         <f t="array" ref="E5">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A5,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F5" s="12" t="str" cm="1">
+      <c r="F5" s="7" t="str" cm="1">
         <f t="array" ref="F5">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A5,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="G5" s="12" t="str" cm="1">
+      <c r="G5" s="7" t="str" cm="1">
         <f t="array" ref="G5">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A5,s003_insights!A:A,0)),"")</f>
         <v>TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" ht="51" spans="1:11">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="12" t="str" cm="1">
+      <c r="E6" s="7" t="str" cm="1">
         <f t="array" ref="E6">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A6,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="12" t="str" cm="1">
+      <c r="F6" s="7" t="str" cm="1">
         <f t="array" ref="F6">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A6,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G6" s="12" t="str" cm="1">
+      <c r="G6" s="7" t="str" cm="1">
         <f t="array" ref="G6">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A6,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="152" spans="1:11">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="12" t="str" cm="1">
+      <c r="E7" s="7" t="str" cm="1">
         <f t="array" ref="E7">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A7,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="F7" s="12" t="str" cm="1">
+      <c r="F7" s="7" t="str" cm="1">
         <f t="array" ref="F7">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A7,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="G7" s="12" t="str" cm="1">
+      <c r="G7" s="7" t="str" cm="1">
         <f t="array" ref="G7">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A7,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" ht="168" spans="1:11">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="12" t="str" cm="1">
+      <c r="E8" s="7" t="str" cm="1">
         <f t="array" ref="E8">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A8,s001_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F8" s="12" t="str" cm="1">
+      <c r="F8" s="7" t="str" cm="1">
         <f t="array" ref="F8">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A8,s002_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="G8" s="12" t="str" cm="1">
+      <c r="G8" s="7" t="str" cm="1">
         <f t="array" ref="G8">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A8,s003_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="23" t="s">
         <v>37</v>
       </c>
       <c r="J8" t="s">
@@ -3739,92 +4483,92 @@
       </c>
     </row>
     <row r="9" ht="101" spans="1:11">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="12" t="str" cm="1">
+      <c r="E9" s="7" t="str" cm="1">
         <f t="array" ref="E9">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A9,s001_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="F9" s="12" t="str" cm="1">
+      <c r="F9" s="7" t="str" cm="1">
         <f t="array" ref="F9">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A9,s002_insights!A:A,0)),"")</f>
         <v>TK06 Trained Sensory and Perceptual Recognition
 TK07 Embodied Posture, Balance, and Spatial Control
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G9" s="12" t="str" cm="1">
+      <c r="G9" s="7" t="str" cm="1">
         <f t="array" ref="G9">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A9,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="23"/>
       <c r="J9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="118" spans="1:11">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="12" t="str" cm="1">
+      <c r="E10" s="7" t="str" cm="1">
         <f t="array" ref="E10">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A10,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="F10" s="12" t="str" cm="1">
+      <c r="F10" s="7" t="str" cm="1">
         <f t="array" ref="F10">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A10,s002_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G10" s="12" t="str" cm="1">
+      <c r="G10" s="7" t="str" cm="1">
         <f t="array" ref="G10">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A10,s003_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment
 TK09 Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I10" s="22"/>
+      <c r="I10" s="23"/>
       <c r="J10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="219" spans="1:11">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="12" t="str" cm="1">
+      <c r="E11" s="7" t="str" cm="1">
         <f t="array" ref="E11">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A11,s001_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
@@ -3833,195 +4577,567 @@
 TK11 Informal Coordination, Communication, and Escalation Know-how
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="F11" s="12" t="str" cm="1">
+      <c r="F11" s="7" t="str" cm="1">
         <f t="array" ref="F11">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A11,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="G11" s="12" t="str" cm="1">
+      <c r="G11" s="7" t="str" cm="1">
         <f t="array" ref="G11">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A11,s003_insights!A:A,0)),"")</f>
         <v>TK09 Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="1" t="s">
+      <c r="I11" s="23"/>
+      <c r="J11" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" ht="135" spans="1:11">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="12" t="str" cm="1">
+      <c r="E12" s="7" t="str" cm="1">
         <f t="array" ref="E12">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A12,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="12" t="str" cm="1">
+      <c r="F12" s="7" t="str" cm="1">
         <f t="array" ref="F12">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A12,s002_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how
 TK09 Shared Professional Language and Contextual Meaning
 TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="G12" s="12" t="str" cm="1">
+      <c r="G12" s="7" t="str" cm="1">
         <f t="array" ref="G12">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A12,s003_insights!A:A,0)),"")</f>
         <v>TK02 Knowledge Conveyed Through Examples or Demonstration
 TK04 Unrecognized or Unarticulated Personal Know-how
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="23"/>
       <c r="J12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" ht="84" spans="1:11">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="12" t="str" cm="1">
+      <c r="E13" s="7" t="str" cm="1">
         <f t="array" ref="E13">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A13,s001_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK11 Informal Coordination, Communication, and Escalation Know-how</v>
       </c>
-      <c r="F13" s="12" t="str" cm="1">
+      <c r="F13" s="7" t="str" cm="1">
         <f t="array" ref="F13">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A13,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="G13" s="12" t="str" cm="1">
+      <c r="G13" s="7" t="str" cm="1">
         <f t="array" ref="G13">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A13,s003_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I13" s="22"/>
+      <c r="I13" s="23"/>
       <c r="J13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" ht="84" spans="1:11">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="12" t="str" cm="1">
+      <c r="E14" s="7" t="str" cm="1">
         <f t="array" ref="E14">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A14,s001_insights!A:A,0)),"")</f>
         <v>TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="F14" s="12" t="str" cm="1">
+      <c r="F14" s="7" t="str" cm="1">
         <f t="array" ref="F14">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A14,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK10 Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="G14" s="12" t="str" cm="1">
+      <c r="G14" s="7" t="str" cm="1">
         <f t="array" ref="G14">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A14,s003_insights!A:A,0)),"")</f>
         <v>TK12 Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I14" s="22"/>
+      <c r="I14" s="23"/>
       <c r="J14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15" ht="84" spans="1:11">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="12" t="str" cm="1">
+      <c r="E15" s="7" t="str" cm="1">
         <f t="array" ref="E15">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A15,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="12" t="str" cm="1">
+      <c r="F15" s="7" t="str" cm="1">
         <f t="array" ref="F15">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A15,s002_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="12" t="str" cm="1">
+      <c r="G15" s="7" t="str" cm="1">
         <f t="array" ref="G15">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A15,s003_insights!A:A,0)),"")</f>
         <v>TK04 Unrecognized or Unarticulated Personal Know-how</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I15" s="22"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" ht="84" spans="1:11">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="12" t="str" cm="1">
+      <c r="E16" s="7" t="str" cm="1">
         <f t="array" ref="E16">IFERROR(INDEX(s001_insights!F:F,MATCH("s001M01"&amp;A16,s001_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="12" t="str" cm="1">
+      <c r="F16" s="7" t="str" cm="1">
         <f t="array" ref="F16">IFERROR(INDEX(s002_insights!F:F,MATCH("s002M01"&amp;A16,s002_insights!A:A,0)),"")</f>
         <v>TK05 Practised Motor and Tool-Operation Skill
 TK06 Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="G16" s="12" t="str" cm="1">
+      <c r="G16" s="7" t="str" cm="1">
         <f t="array" ref="G16">IFERROR(INDEX(s003_insights!F:F,MATCH("s003M01"&amp;A16,s003_insights!A:A,0)),"")</f>
         <v/>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="22"/>
+      <c r="I16" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="12.96875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="39.84375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="49.2109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.4375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" ht="135" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="3" ht="68" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" ht="68" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6" ht="68" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" ht="51" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="8" ht="68" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" ht="68" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10" ht="68" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" ht="68" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="12" ht="68" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" ht="68" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="14" ht="68" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="15" ht="68" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="16" ht="68" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="17" ht="68" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="18" ht="68" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="19" ht="68" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="20" ht="68" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="21" ht="68" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="22" ht="68" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="23" ht="68" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="24" ht="84" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="25" ht="68" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>496</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4043,324 +5159,324 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.5" spans="1:7">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" ht="51" spans="1:7">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="25" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:7">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="25" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="51" spans="1:7">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="25" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" ht="51" spans="1:7">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="25" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="6" ht="63" spans="1:7">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="25" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" ht="63" spans="1:7">
-      <c r="A7" s="21" t="s">
+    <row r="7" ht="51" spans="1:7">
+      <c r="A7" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" ht="51" spans="1:7">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="25" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="9" ht="51" spans="1:7">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="G9" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" ht="78" spans="1:7">
-      <c r="A10" s="21" t="s">
+    <row r="10" ht="63" spans="1:7">
+      <c r="A10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="25" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="11" ht="51" spans="1:7">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="12" ht="63" spans="1:7">
-      <c r="A12" s="21" t="s">
+    <row r="12" ht="51" spans="1:7">
+      <c r="A12" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="25" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="13" ht="51" spans="1:7">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="25" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="14" ht="34.75" spans="1:7">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="26" t="s">
         <v>109</v>
       </c>
     </row>
@@ -4377,35 +5493,35 @@
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="15.4921875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="24.734375" style="14" customWidth="1"/>
-    <col min="3" max="4" width="30.7265625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="35.6796875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="48.953125" style="14" customWidth="1"/>
-    <col min="7" max="7" width="45.5703125" style="14" customWidth="1"/>
+    <col min="1" max="1" width="15.4921875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="24.734375" style="15" customWidth="1"/>
+    <col min="3" max="4" width="30.7265625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="35.6796875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="48.953125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="45.5703125" style="15" customWidth="1"/>
     <col min="9" max="9" width="26.6015625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:9">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -4416,292 +5532,292 @@
       </c>
     </row>
     <row r="2" ht="84" spans="1:9">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="19">
+      <c r="H2" s="20">
         <f t="shared" ref="H2:H11" si="0">3-COUNTIF(E2:G2,"")</f>
         <v>2</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" ht="152" customHeight="1" spans="1:9">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" ht="185" spans="1:9">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="5" ht="135" spans="1:9">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" ht="101" spans="1:9">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="19">
+      <c r="G6" s="17"/>
+      <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" ht="68" spans="1:9">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" ht="152" customHeight="1" spans="1:9">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="16" t="s">
+      <c r="E8" s="18"/>
+      <c r="F8" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" ht="168" spans="1:9">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" ht="84" spans="1:9">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16" t="s">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="11" ht="84" spans="1:9">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4723,281 +5839,281 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="25.3046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.0546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="25.3046875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="25.0546875" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.09375" customWidth="1"/>
     <col min="5" max="5" width="41.671875" customWidth="1"/>
-    <col min="6" max="6" width="45.9375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.9375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:6">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:6">
-      <c r="A2" s="12" t="str">
+      <c r="A2" s="7" t="str">
         <f>cross_sector_insights_tk!A2</f>
         <v>TK02</v>
       </c>
-      <c r="B2" s="12" t="str">
+      <c r="B2" s="7" t="str">
         <f>cross_sector_insights_tk!B2</f>
         <v>Knowledge Conveyed Through Examples or Demonstration</v>
       </c>
-      <c r="C2" s="12" t="str">
+      <c r="C2" s="7" t="str">
         <f>cross_sector_insights_tk!D2</f>
         <v>Relational Tacit Knowledge</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="9" t="str">
         <f>cross_sector_insights_tk!H2&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E2" s="13" t="str">
+      <c r="E2" s="9" t="str">
         <f>cross_sector_insights_tk!I2</f>
         <v>Manufacturing; Health Services</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:6">
-      <c r="A3" s="12" t="str">
+      <c r="A3" s="7" t="str">
         <f>cross_sector_insights_tk!A3</f>
         <v>TK04</v>
       </c>
-      <c r="B3" s="12" t="str">
+      <c r="B3" s="7" t="str">
         <f>cross_sector_insights_tk!B3</f>
         <v>Unrecognized or Unarticulated Personal Know-how</v>
       </c>
-      <c r="C3" s="12" t="str">
+      <c r="C3" s="7" t="str">
         <f>cross_sector_insights_tk!D3</f>
         <v>Relational Tacit Knowledge</v>
       </c>
-      <c r="D3" s="13" t="str">
+      <c r="D3" s="9" t="str">
         <f>cross_sector_insights_tk!H3&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E3" s="13" t="str">
+      <c r="E3" s="9" t="str">
         <f>cross_sector_insights_tk!I3</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:6">
-      <c r="A4" s="12" t="str">
+      <c r="A4" s="7" t="str">
         <f>cross_sector_insights_tk!A4</f>
         <v>TK05</v>
       </c>
-      <c r="B4" s="12" t="str">
+      <c r="B4" s="7" t="str">
         <f>cross_sector_insights_tk!B4</f>
         <v>Practised Motor and Tool-Operation Skill</v>
       </c>
-      <c r="C4" s="12" t="str">
+      <c r="C4" s="7" t="str">
         <f>cross_sector_insights_tk!D4</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D4" s="13" t="str">
+      <c r="D4" s="9" t="str">
         <f>cross_sector_insights_tk!H4&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E4" s="13" t="str">
+      <c r="E4" s="9" t="str">
         <f>cross_sector_insights_tk!I4</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:6">
-      <c r="A5" s="12" t="str">
+      <c r="A5" s="7" t="str">
         <f>cross_sector_insights_tk!A5</f>
         <v>TK06</v>
       </c>
-      <c r="B5" s="12" t="str">
+      <c r="B5" s="7" t="str">
         <f>cross_sector_insights_tk!B5</f>
         <v>Trained Sensory and Perceptual Recognition</v>
       </c>
-      <c r="C5" s="12" t="str">
+      <c r="C5" s="7" t="str">
         <f>cross_sector_insights_tk!D5</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D5" s="13" t="str">
+      <c r="D5" s="9" t="str">
         <f>cross_sector_insights_tk!H5&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E5" s="13" t="str">
+      <c r="E5" s="9" t="str">
         <f>cross_sector_insights_tk!I5</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:6">
-      <c r="A6" s="12" t="str">
+      <c r="A6" s="7" t="str">
         <f>cross_sector_insights_tk!A6</f>
         <v>TK07</v>
       </c>
-      <c r="B6" s="12" t="str">
+      <c r="B6" s="7" t="str">
         <f>cross_sector_insights_tk!B6</f>
         <v>Embodied Posture, Balance, and Spatial Control</v>
       </c>
-      <c r="C6" s="12" t="str">
+      <c r="C6" s="7" t="str">
         <f>cross_sector_insights_tk!D6</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D6" s="13" t="str">
+      <c r="D6" s="9" t="str">
         <f>cross_sector_insights_tk!H6&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E6" s="13" t="str">
+      <c r="E6" s="9" t="str">
         <f>cross_sector_insights_tk!I6</f>
         <v>Construction; Manufacturing</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="7" ht="51" spans="1:6">
-      <c r="A7" s="12" t="str">
+      <c r="A7" s="7" t="str">
         <f>cross_sector_insights_tk!A7</f>
         <v>TK08</v>
       </c>
-      <c r="B7" s="12" t="str">
+      <c r="B7" s="7" t="str">
         <f>cross_sector_insights_tk!B7</f>
         <v>Immediate Embodied Response to Changing Conditions</v>
       </c>
-      <c r="C7" s="12" t="str">
+      <c r="C7" s="7" t="str">
         <f>cross_sector_insights_tk!D7</f>
         <v>Somatic Tacit Knowledge</v>
       </c>
-      <c r="D7" s="13" t="str">
+      <c r="D7" s="9" t="str">
         <f>cross_sector_insights_tk!H7&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E7" s="13" t="str">
+      <c r="E7" s="9" t="str">
         <f>cross_sector_insights_tk!I7</f>
         <v>Construction; Health Services</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="8" ht="34" spans="1:6">
-      <c r="A8" s="12" t="str">
+      <c r="A8" s="7" t="str">
         <f>cross_sector_insights_tk!A8</f>
         <v>TK09</v>
       </c>
-      <c r="B8" s="12" t="str">
+      <c r="B8" s="7" t="str">
         <f>cross_sector_insights_tk!B8</f>
         <v>Shared Professional Language and Contextual Meaning</v>
       </c>
-      <c r="C8" s="12" t="str">
+      <c r="C8" s="7" t="str">
         <f>cross_sector_insights_tk!D8</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D8" s="13" t="str">
+      <c r="D8" s="9" t="str">
         <f>cross_sector_insights_tk!H8&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E8" s="13" t="str">
+      <c r="E8" s="9" t="str">
         <f>cross_sector_insights_tk!I8</f>
         <v>Manufacturing; Health Services</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="9" ht="34" spans="1:6">
-      <c r="A9" s="12" t="str">
+      <c r="A9" s="7" t="str">
         <f>cross_sector_insights_tk!A9</f>
         <v>TK10</v>
       </c>
-      <c r="B9" s="12" t="str">
+      <c r="B9" s="7" t="str">
         <f>cross_sector_insights_tk!B9</f>
         <v>Shared Professional Norms and Standards of Judgment</v>
       </c>
-      <c r="C9" s="12" t="str">
+      <c r="C9" s="7" t="str">
         <f>cross_sector_insights_tk!D9</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D9" s="13" t="str">
+      <c r="D9" s="9" t="str">
         <f>cross_sector_insights_tk!H9&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E9" s="13" t="str">
+      <c r="E9" s="9" t="str">
         <f>cross_sector_insights_tk!I9</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="10" ht="51" spans="1:6">
-      <c r="A10" s="12" t="str">
+      <c r="A10" s="7" t="str">
         <f>cross_sector_insights_tk!A10</f>
         <v>TK11</v>
       </c>
-      <c r="B10" s="12" t="str">
+      <c r="B10" s="7" t="str">
         <f>cross_sector_insights_tk!B10</f>
         <v>Informal Coordination, Communication, and Escalation Know-how</v>
       </c>
-      <c r="C10" s="12" t="str">
+      <c r="C10" s="7" t="str">
         <f>cross_sector_insights_tk!D10</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D10" s="13" t="str">
+      <c r="D10" s="9" t="str">
         <f>cross_sector_insights_tk!H10&amp;"/3"</f>
         <v>2/3</v>
       </c>
-      <c r="E10" s="13" t="str">
+      <c r="E10" s="9" t="str">
         <f>cross_sector_insights_tk!I10</f>
         <v>Construction; Health Services</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:6">
-      <c r="A11" s="12" t="str">
+      <c r="A11" s="7" t="str">
         <f>cross_sector_insights_tk!A11</f>
         <v>TK12</v>
       </c>
-      <c r="B11" s="12" t="str">
+      <c r="B11" s="7" t="str">
         <f>cross_sector_insights_tk!B11</f>
         <v>Organizational Culture and Unwritten Working Practices</v>
       </c>
-      <c r="C11" s="12" t="str">
+      <c r="C11" s="7" t="str">
         <f>cross_sector_insights_tk!D11</f>
         <v>Collective Tacit Knowledge</v>
       </c>
-      <c r="D11" s="13" t="str">
+      <c r="D11" s="9" t="str">
         <f>cross_sector_insights_tk!H11&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="E11" s="13" t="str">
+      <c r="E11" s="9" t="str">
         <f>cross_sector_insights_tk!I11</f>
         <v>Construction; Manufacturing; Health Services</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="7" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5013,266 +6129,266 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="25.515625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="23.171875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="50.515625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="32.9375" style="10" customWidth="1"/>
-    <col min="7" max="7" width="23.0390625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.4375" style="9"/>
+    <col min="1" max="1" width="12.109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="25.515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="23.171875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="50.515625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="32.9375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="23.0390625" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="8.4375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" ht="17" spans="1:8">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="13" customFormat="1" ht="17" spans="1:8">
+      <c r="A1" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="2" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A2" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="14" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="3" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A3" s="9" t="s">
+    <row r="3" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A3" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A4" s="9" t="s">
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A4" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A5" s="9" t="s">
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A5" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A6" s="9" t="s">
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A6" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="H6" s="10"/>
-    </row>
-    <row r="7" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A7" s="9" t="s">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A7" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="14" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="8" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A8" s="9" t="s">
+    <row r="8" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A8" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A9" s="9" t="s">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A9" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10" s="9" customFormat="1" ht="409.5" spans="1:8">
-      <c r="A10" s="9" t="s">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" s="13" customFormat="1" ht="409.5" spans="1:8">
+      <c r="A10" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" s="9" customFormat="1" spans="1:8">
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-    </row>
-    <row r="12" s="9" customFormat="1" spans="1:8">
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" s="13" customFormat="1" spans="1:8">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" s="13" customFormat="1" spans="1:8">
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5286,293 +6402,293 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="19.0078125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="24.8671875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="27.8671875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.0390625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="41.1484375" style="9" customWidth="1"/>
-    <col min="7" max="16384" width="8.4375" style="9"/>
+    <col min="1" max="1" width="16.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="19.0078125" style="13" customWidth="1"/>
+    <col min="3" max="3" width="24.8671875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="27.8671875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="26.0390625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="41.1484375" style="13" customWidth="1"/>
+    <col min="7" max="16384" width="8.4375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:7">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="13" customFormat="1" spans="1:7">
+      <c r="A1" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="13" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="2" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A2" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="13" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="3" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A3" s="9" t="s">
+    <row r="3" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A3" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="13" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A4" s="9" t="s">
+    <row r="4" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A4" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="13" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="5" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A5" s="9" t="s">
+    <row r="5" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A5" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="13" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="6" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A6" s="9" t="s">
+    <row r="6" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A6" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="13" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="7" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A7" s="9" t="s">
+    <row r="7" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A7" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="13" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A8" s="9" t="s">
+    <row r="8" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A8" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="13" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="9" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A9" s="9" t="s">
+    <row r="9" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A9" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="13" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="10" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A10" s="9" t="s">
+    <row r="10" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A10" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="13" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="11" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A11" s="9" t="s">
+    <row r="11" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A11" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="13" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="12" s="9" customFormat="1" ht="409.5" spans="1:7">
-      <c r="A12" s="9" t="s">
+    <row r="12" s="13" customFormat="1" ht="409.5" spans="1:7">
+      <c r="A12" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="13" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="19" spans="6:6">
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="13" t="s">
         <v>285</v>
       </c>
     </row>
@@ -5625,7 +6741,7 @@
       <c r="B2" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>287</v>
       </c>
       <c r="D2" t="s">
@@ -5634,7 +6750,7 @@
       <c r="E2" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>289</v>
       </c>
       <c r="G2" t="s">
@@ -5648,7 +6764,7 @@
       <c r="B3" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>292</v>
       </c>
       <c r="D3" t="s">
@@ -5671,7 +6787,7 @@
       <c r="B4" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>296</v>
       </c>
       <c r="D4" t="s">
@@ -5680,7 +6796,7 @@
       <c r="E4" t="s">
         <v>297</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G4" t="s">
@@ -5694,7 +6810,7 @@
       <c r="B5" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>301</v>
       </c>
       <c r="D5" t="s">
@@ -5717,7 +6833,7 @@
       <c r="B6" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>305</v>
       </c>
       <c r="D6" t="s">
@@ -5726,7 +6842,7 @@
       <c r="E6" t="s">
         <v>306</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="5" t="s">
         <v>307</v>
       </c>
       <c r="G6" t="s">
@@ -5740,7 +6856,7 @@
       <c r="B7" t="s">
         <v>188</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>310</v>
       </c>
       <c r="D7" t="s">
@@ -5749,7 +6865,7 @@
       <c r="E7" t="s">
         <v>311</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>212</v>
       </c>
       <c r="G7" t="s">
@@ -5763,7 +6879,7 @@
       <c r="B8" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>314</v>
       </c>
       <c r="D8" t="s">
@@ -5772,7 +6888,7 @@
       <c r="E8" t="s">
         <v>315</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="5" t="s">
         <v>316</v>
       </c>
       <c r="G8" t="s">
@@ -5786,7 +6902,7 @@
       <c r="B9" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>319</v>
       </c>
       <c r="D9" t="s">
@@ -5809,7 +6925,7 @@
       <c r="B10" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="5" t="s">
         <v>324</v>
       </c>
       <c r="D10" t="s">
@@ -5832,7 +6948,7 @@
       <c r="B11" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="5" t="s">
         <v>328</v>
       </c>
       <c r="D11" t="s">
@@ -5871,13 +6987,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="10" t="s">
         <v>334</v>
       </c>
       <c r="D1" t="s">
@@ -5885,86 +7001,89 @@
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:8">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:8">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>349</v>
       </c>
+      <c r="H3" s="5" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="4" ht="409.5" spans="1:8">
-      <c r="A4" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="E4" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" ht="409.5" spans="1:8">
       <c r="A5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>356</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="6" ht="409.5" spans="1:8">
       <c r="A6" t="s">
-        <v>357</v>
-      </c>
-      <c r="D6" s="8" t="s">
         <v>358</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5979,206 +7098,206 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="17.578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="55.3359375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="55.3359375" style="5" customWidth="1"/>
     <col min="3" max="3" width="32.9453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>361</v>
       </c>
+      <c r="C1" s="6" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="2" ht="17" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
-      <c r="A13" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>344</v>
       </c>
     </row>
